--- a/examples/300476_胜宏科技_估值模型.xlsx
+++ b/examples/300476_胜宏科技_估值模型.xlsx
@@ -19,12 +19,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
+    <definedName name="WACC_USED">Assumptions!$C$90</definedName>
+    <definedName name="WACC_CALC">Assumptions!$C$88</definedName>
+    <definedName name="TERM_G">Assumptions!$C$91</definedName>
+    <definedName name="KE">Assumptions!$C$86</definedName>
+    <definedName name="KD">Assumptions!$C$87</definedName>
+    <definedName name="RF_RATE">Assumptions!$C$79</definedName>
+    <definedName name="ERP">Assumptions!$C$80</definedName>
+    <definedName name="BETA_U">Assumptions!$C$81</definedName>
+    <definedName name="TAX_RATE_Y1">Assumptions!$C$41</definedName>
+    <definedName name="PAYOUT_Y1">Assumptions!$C$61</definedName>
+    <definedName name="MIN_CASH_PCT">Assumptions!$C$65</definedName>
+    <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
+    <definedName name="DCF_PS">DCF!$D$25</definedName>
+    <definedName name="FCFE_PS">FCFE!$D$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -872,7 +889,7 @@
         </is>
       </c>
       <c r="C24" s="4">
-        <f>TEXT(Summary!C11,"0.00")&amp;" ~ "&amp;TEXT(Summary!D11,"0.00")</f>
+        <f>TEXT(Summary!C12,"0.00")&amp;" ~ "&amp;TEXT(Summary!D12,"0.00")</f>
         <v/>
       </c>
     </row>
@@ -883,7 +900,7 @@
         </is>
       </c>
       <c r="C25" s="4">
-        <f>Checks!F22</f>
+        <f>Checks!F24</f>
         <v/>
       </c>
     </row>
@@ -5882,6 +5899,487 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>胜宏科技 — FCFE 股权自由现金流估值 (Ke折现, 与FCFF双视图)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得股权价值, 无需EV→Equity桥</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>归母净利润</t>
+        </is>
+      </c>
+      <c r="E4" s="26">
+        <f>IS!E20</f>
+        <v/>
+      </c>
+      <c r="F4" s="26">
+        <f>IS!F20</f>
+        <v/>
+      </c>
+      <c r="G4" s="26">
+        <f>IS!G20</f>
+        <v/>
+      </c>
+      <c r="H4" s="26">
+        <f>IS!H20</f>
+        <v/>
+      </c>
+      <c r="I4" s="26">
+        <f>IS!I20</f>
+        <v/>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>＝IS归母净利(含FIN调度后的利息)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>加: D&amp;A</t>
+        </is>
+      </c>
+      <c r="E5" s="26">
+        <f>PPE!E19</f>
+        <v/>
+      </c>
+      <c r="F5" s="26">
+        <f>PPE!F19</f>
+        <v/>
+      </c>
+      <c r="G5" s="26">
+        <f>PPE!G19</f>
+        <v/>
+      </c>
+      <c r="H5" s="26">
+        <f>PPE!H19</f>
+        <v/>
+      </c>
+      <c r="I5" s="26">
+        <f>PPE!I19</f>
+        <v/>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>＝PP&amp;E页折旧+无形摊销</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>减: ΔNWC</t>
+        </is>
+      </c>
+      <c r="E6" s="26">
+        <f>Schedules!E18</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>Schedules!F18</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>Schedules!G18</f>
+        <v/>
+      </c>
+      <c r="H6" s="26">
+        <f>Schedules!H18</f>
+        <v/>
+      </c>
+      <c r="I6" s="26">
+        <f>Schedules!I18</f>
+        <v/>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>＝Schedules; NWC增加为现金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>减: Capex</t>
+        </is>
+      </c>
+      <c r="E7" s="26">
+        <f>PPE!E14</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>PPE!F14</f>
+        <v/>
+      </c>
+      <c r="G7" s="26">
+        <f>PPE!G14</f>
+        <v/>
+      </c>
+      <c r="H7" s="26">
+        <f>PPE!H14</f>
+        <v/>
+      </c>
+      <c r="I7" s="26">
+        <f>PPE!I14</f>
+        <v/>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>＝PP&amp;E页资本开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>加: 净新增借款</t>
+        </is>
+      </c>
+      <c r="E8" s="26">
+        <f>FIN!E57</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>FIN!F57</f>
+        <v/>
+      </c>
+      <c r="G8" s="26">
+        <f>FIN!G57</f>
+        <v/>
+      </c>
+      <c r="H8" s="26">
+        <f>FIN!H57</f>
+        <v/>
+      </c>
+      <c r="I8" s="26">
+        <f>FIN!I57</f>
+        <v/>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>＝FIN四档债务期末-期初(revolver新增-sweep偿还-计划还款); 股权口径下债务净变动归股东</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>FCFE</t>
+        </is>
+      </c>
+      <c r="E9" s="35">
+        <f>E4+E5-E6-E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="35">
+        <f>F4+F5-F6-F7+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="35">
+        <f>G4+G5-G6-G7+G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="35">
+        <f>H4+H5-H6-H7+H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="35">
+        <f>I4+I5-I6-I7+I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>＝归母+D&amp;A-ΔNWC-Capex+净新增借款</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>折现年序(年中)</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" s="41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>年中折现, 与DCF页同口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>折现因子 (Ke)</t>
+        </is>
+      </c>
+      <c r="E11" s="31">
+        <f>1/(1+KE)^E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="31">
+        <f>1/(1+KE)^F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>1/(1+KE)^G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>1/(1+KE)^H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="31">
+        <f>1/(1+KE)^I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PV(FCFE)</t>
+        </is>
+      </c>
+      <c r="E12" s="26">
+        <f>E9*E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>F9*F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="26">
+        <f>G9*G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="26">
+        <f>H9*H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="26">
+        <f>I9*I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>显性期PV合计 (2026-2030)</t>
+        </is>
+      </c>
+      <c r="D14" s="35">
+        <f>SUM(E12:I12)</f>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>终值 TV (Gordon)</t>
+        </is>
+      </c>
+      <c r="D15" s="26">
+        <f>I9*(1+TERM_G)/(KE-TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>＝FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PV(终值)</t>
+        </is>
+      </c>
+      <c r="D16" s="26">
+        <f>D15*I11</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>终值按t=4.5折现(与DCF页一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>股权价值 (FCFE口径)</t>
+        </is>
+      </c>
+      <c r="D17" s="35">
+        <f>D14+D16</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>FCFE直接折现为股权价值, 无需净现金桥</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D18" s="15">
+        <f>D17/SHARES_DIL</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/稀释股数(named range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>对照: FCFF口径每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>DCF!D25</f>
+        <v/>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>＝DCF页主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>两法差异 (FCFE/FCFF-1)</t>
+        </is>
+      </c>
+      <c r="D20" s="42">
+        <f>D18/D19-1</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Checks页含一致性信息行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>两法差异原因</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债, FCFE已含净新增借款、直接对应股权; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6474,7 +6972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7004,7 +7502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7755,13 +8253,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8182,132 +8680,168 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>信息项: 隐含折旧率(折旧/期初固资净值)</t>
-        </is>
-      </c>
-      <c r="E16" s="55">
-        <f>PPE!E20</f>
-        <v/>
-      </c>
-      <c r="F16" s="55">
-        <f>PPE!F20</f>
-        <v/>
-      </c>
-      <c r="G16" s="55">
-        <f>PPE!G20</f>
-        <v/>
-      </c>
-      <c r="H16" s="55">
-        <f>PPE!H20</f>
-        <v/>
-      </c>
-      <c r="I16" s="55">
-        <f>PPE!I20</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>信息行: 合理带宽8%-18%</t>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12. Named ranges存在性 (审计轨迹, 15个)</t>
+        </is>
+      </c>
+      <c r="B15" s="54">
+        <f>AND(ISNUMBER(INDIRECT("SCEN_SWITCH")),ISNUMBER(INDIRECT("WACC_USED")),ISNUMBER(INDIRECT("WACC_CALC")),ISNUMBER(INDIRECT("TERM_G")),ISNUMBER(INDIRECT("KE")),ISNUMBER(INDIRECT("KD")),ISNUMBER(INDIRECT("RF_RATE")),ISNUMBER(INDIRECT("ERP")),ISNUMBER(INDIRECT("BETA_U")),ISNUMBER(INDIRECT("TAX_RATE_Y1")),ISNUMBER(INDIRECT("PAYOUT_Y1")),ISNUMBER(INDIRECT("MIN_CASH_PCT")),ISNUMBER(INDIRECT("SHARES_DIL")),ISNUMBER(INDIRECT("DCF_PS")),ISNUMBER(INDIRECT("FCFE_PS")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>WACC采用值/永续g/Ke/Kd/rf/ERP/βu/税率/股利/最低现金/情景开关/稀释股数/DCF&amp;FCFE每股; 任一named range被删则FALSE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>信息项: 2026E模型收入/一致预期</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>IS!E4/Assumptions!$C$12</f>
+          <t>信息项: 隐含折旧率(折旧/期初固资净值)</t>
+        </is>
+      </c>
+      <c r="E17" s="55">
+        <f>PPE!E20</f>
+        <v/>
+      </c>
+      <c r="F17" s="55">
+        <f>PPE!F20</f>
+        <v/>
+      </c>
+      <c r="G17" s="55">
+        <f>PPE!G20</f>
+        <v/>
+      </c>
+      <c r="H17" s="55">
+        <f>PPE!H20</f>
+        <v/>
+      </c>
+      <c r="I17" s="55">
+        <f>PPE!I20</f>
         <v/>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>接近100%即基准贴合一致预期</t>
+          <t>信息行: 合理带宽8%-18%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>信息项: 2026E模型归母/一致预期</t>
+          <t>信息项: 2026E模型收入/一致预期</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>IS!E20/Assumptions!$C$13</f>
-        <v/>
+        <f>IS!E4/Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>接近100%即基准贴合一致预期</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>信息项: WACC计算值/采用值</t>
+          <t>信息项: 2026E模型归母/一致预期</t>
         </is>
       </c>
       <c r="B19" s="16">
-        <f>Assumptions!C88</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>Assumptions!C90</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>左=计算值, 右=采用值(override为空时两者相等)</t>
-        </is>
+        <f>IS!E20/Assumptions!$C$13</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>信息项: WACC计算值/采用值</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>Assumptions!C88</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>Assumptions!C90</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>左=计算值, 右=采用值(override为空时两者相等)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>信息项: FCFE/FCFF每股价值比</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>FCFE!D18/DCF!D25</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>FCFE!D18</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>左=FCFE/FCFF比值, 右=FCFE每股(元); 两法差异原因见FCFE页底部注记</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>信息项: 2030E现金 vs 最低现金</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B22" s="26">
         <f>BS!I4</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C22" s="26">
         <f>FIN!I13</f>
         <v/>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>两者应相等(sweep后现金=最低现金, 溢出去理财)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="56" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">汇总: 全部通过 = </t>
         </is>
       </c>
-      <c r="F22" s="57">
-        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14),"全部通过=TRUE","存在未通过=FALSE")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="F24" s="57">
+        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>布尔汇总</t>
         </is>
       </c>
-      <c r="F23" s="27">
-        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14)</f>
+      <c r="F25" s="27">
+        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8320,7 +8854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8551,147 +9085,192 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>现价 (2026-08-14)</t>
+          <t>FCFE股权现金流 — 基准</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ke折现(股权口径)</t>
         </is>
       </c>
       <c r="C10" s="14">
-        <f>Assumptions!$C$7</f>
+        <f>FCFE!D18</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="E10" s="14">
-        <f>Assumptions!$C$7</f>
-        <v/>
+        <f>FCFE!D18</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>(C10+D10)/2</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>E10/Assumptions!$C$7-1</f>
+        <v/>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>FCFE=归母+D&amp;A-ΔNWC-Capex+净新增借款(FIN调度), 与FCFF双视图对照</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>现价 (2026-08-14)</t>
+        </is>
+      </c>
+      <c r="C11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>综合参考区间(全方法包络)</t>
         </is>
       </c>
-      <c r="C11" s="17">
-        <f>MIN(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D11" s="17">
-        <f>MAX(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>(C11+D11)/2</f>
-        <v/>
-      </c>
-      <c r="F11" s="18">
-        <f>E11/Assumptions!$C$7-1</f>
-        <v/>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="C12" s="17">
+        <f>MIN(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>MAX(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>(C12+D12)/2</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>E12/Assumptions!$C$7-1</f>
+        <v/>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>熊简化法DCF下限 ~ 牛简化法/相对估值上限的包络</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>区间可视化 (每个▮≈10元, 起点=区间低值)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>区间条(低→高, 括号为现价相对位置)</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>DCF绝对估值 — 基准</t>
-        </is>
-      </c>
-      <c r="B15" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>DCF绝对估值 — 熊市</t>
+          <t>DCF绝对估值 — 基准</t>
         </is>
       </c>
       <c r="B16" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>DCF绝对估值 — 牛市</t>
+          <t>DCF绝对估值 — 熊市</t>
         </is>
       </c>
       <c r="B17" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>相对估值 — 模型2026E归母</t>
+          <t>DCF绝对估值 — 牛市</t>
         </is>
       </c>
       <c r="B18" s="20">
-        <f>REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
+        <f>REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t>相对估值 — 模型2026E归母</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t>相对估值 — 一致预期2026E归母</t>
         </is>
       </c>
-      <c r="B19" s="20">
+      <c r="B20" s="20">
         <f>REPT("▮",MAX(1,ROUND((D9-C9)/10,0)))&amp;"  ["&amp;TEXT(C9,"0")&amp;"—"&amp;TEXT(D9,"0")&amp;"]"</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>FCFE股权现金流 — 基准</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>REPT("▮",MAX(1,ROUND((D10-C10)/10,0)))&amp;"  ["&amp;TEXT(C10,"0")&amp;"—"&amp;TEXT(D10,"0")&amp;"]"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>关键假设提示</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>WACC采用值与可比beta联动(Assumptions第十节); 三情景主模型切换见Assumptions情景开关; 校验状态见Checks页</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/300476_胜宏科技_估值模型.xlsx
+++ b/examples/300476_胜宏科技_估值模型.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FIN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
@@ -39,8 +39,8 @@
     <definedName name="PAYOUT_Y1">Assumptions!$C$61</definedName>
     <definedName name="MIN_CASH_PCT">Assumptions!$C$65</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
-    <definedName name="DCF_PS">DCF!$D$25</definedName>
-    <definedName name="FCFE_PS">FCFE!$D$18</definedName>
+    <definedName name="DCF_PS">DCF!$D$26</definedName>
+    <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
 </workbook>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C21" s="4">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5783,101 +5783,117 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>减: 少数股东权益(2025A末)</t>
+        </is>
+      </c>
+      <c r="D23" s="26">
+        <f>-BS!D44</f>
+        <v/>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>EV桥得归母口径股权价值须扣少数股东权益(账面值); 无少数股东权益的标的为0, 不影响结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>净现金调整合计</t>
         </is>
       </c>
-      <c r="D23" s="26">
-        <f>D19+D20+D21+D22</f>
-        <v/>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="D24" s="26">
+        <f>D19+D20+D21+D22+D23</f>
+        <v/>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供Sensitivity/Scenarios页引用</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>股权价值</t>
-        </is>
-      </c>
-      <c r="D24" s="35">
-        <f>D18+D23</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>股权价值</t>
+        </is>
+      </c>
+      <c r="D25" s="35">
+        <f>D18+D24</f>
+        <v/>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>每股价值 (元)</t>
         </is>
       </c>
-      <c r="D25" s="15">
-        <f>D24/Equity_Roll!$C$21</f>
-        <v/>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="D26" s="15">
+        <f>D25/Equity_Roll!$C$21</f>
+        <v/>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>＝股权价值/稀释股数(Equity_Roll页)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>现价 (2026-08-14)</t>
         </is>
       </c>
-      <c r="D26" s="14">
+      <c r="D27" s="14">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>隐含涨跌幅</t>
         </is>
       </c>
-      <c r="D27" s="42">
-        <f>D25/D26-1</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>隐含2026E P/E</t>
-        </is>
-      </c>
-      <c r="D28" s="43">
-        <f>D24/IS!E20</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/2026E归母</t>
-        </is>
-      </c>
+      <c r="D28" s="42">
+        <f>D26/D27-1</f>
+        <v/>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>隐含2026E P/E</t>
+        </is>
+      </c>
+      <c r="D29" s="43">
+        <f>D25/IS!E20</f>
+        <v/>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/2026E归母</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>隐含2026E EV/EBITDA</t>
         </is>
       </c>
-      <c r="D29" s="43">
+      <c r="D30" s="43">
         <f>D18/(IS!E23+PPE!E19)</f>
         <v/>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>注: 估值基准日2026-08-14, 与2026财年现金流起点存在时间错位; 年中折现(t=0.5起)为该错位的标准近似处理, 不再单独做stub调整</t>
         </is>
@@ -5886,7 +5902,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5899,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5924,7 +5940,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得股权价值, 无需EV→Equity桥</t>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
         </is>
       </c>
     </row>
@@ -6126,248 +6142,296 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>理财净变动(勾稽参考, 不计入FCFE)</t>
+        </is>
+      </c>
+      <c r="E9" s="26">
+        <f>-FIN!E62</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>-FIN!F62</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>-FIN!G62</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>-FIN!H62</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>-FIN!I62</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>＝-FIN理财净变动: sweep溢出购买理财为现金↔理财的形态转换(资产仍在表内归属股东), 故不计入FCFE; 显性列示供FCFE↔FCFF差异勾稽(FCFF也未扣理财购买, 两法在此口径一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>FCFE</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E10" s="35">
         <f>E4+E5-E6-E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F10" s="35">
         <f>F4+F5-F6-F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G10" s="35">
         <f>G4+G5-G6-G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H10" s="35">
         <f>H4+H5-H6-H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I10" s="35">
         <f>I4+I5-I6-I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>＝归母+D&amp;A-ΔNWC-Capex+净新增借款</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>折现年序(年中)</t>
-        </is>
-      </c>
-      <c r="E10" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H10" s="41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I10" s="41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>折现因子 (Ke)</t>
-        </is>
-      </c>
-      <c r="E11" s="31">
-        <f>1/(1+KE)^E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="31">
-        <f>1/(1+KE)^F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="31">
-        <f>1/(1+KE)^G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="31">
-        <f>1/(1+KE)^H10</f>
-        <v/>
-      </c>
-      <c r="I11" s="31">
-        <f>1/(1+KE)^I10</f>
-        <v/>
+          <t>折现年序(年中)</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="41" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>折现因子 (Ke)</t>
+        </is>
+      </c>
+      <c r="E12" s="31">
+        <f>1/(1+KE)^E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>1/(1+KE)^F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>1/(1+KE)^G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>1/(1+KE)^H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="31">
+        <f>1/(1+KE)^I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>PV(FCFE)</t>
         </is>
       </c>
-      <c r="E12" s="26">
-        <f>E9*E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>F9*F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>G9*G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="26">
-        <f>H9*H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
-        <f>I9*I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="E13" s="26">
+        <f>E10*E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>F10*F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>G10*G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="26">
+        <f>H10*H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="26">
+        <f>I10*I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>显性期PV合计 (2026-2030)</t>
         </is>
       </c>
-      <c r="D14" s="35">
-        <f>SUM(E12:I12)</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>终值 TV (Gordon)</t>
-        </is>
-      </c>
-      <c r="D15" s="26">
-        <f>I9*(1+TERM_G)/(KE-TERM_G)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>＝FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
-        </is>
-      </c>
+      <c r="D15" s="35">
+        <f>SUM(E13:I13)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>正常化FCFE (2030E, 终值口径)</t>
+        </is>
+      </c>
+      <c r="D16" s="26">
+        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>终值 TV (Gordon, 正常化FCFE)</t>
+        </is>
+      </c>
+      <c r="D17" s="26">
+        <f>D16*(1+TERM_G)/(KE-TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>＝正常化FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>PV(终值)</t>
         </is>
       </c>
-      <c r="D16" s="26">
-        <f>D15*I11</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="D18" s="26">
+        <f>D17*I12</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>终值按t=4.5折现(与DCF页一致)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>股权价值 (FCFE口径)</t>
         </is>
       </c>
-      <c r="D17" s="35">
-        <f>D14+D16</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="D19" s="35">
+        <f>D15+D18</f>
+        <v/>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>FCFE直接折现为股权价值, 无需净现金桥</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D18" s="15">
-        <f>D17/SHARES_DIL</f>
-        <v/>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/稀释股数(named range)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>对照: FCFF口径每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D19" s="14">
-        <f>DCF!D25</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>＝DCF页主输出</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D20" s="15">
+        <f>D19/SHARES_DIL</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/稀释股数(named range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>对照: FCFF口径每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>DCF!D26</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>＝DCF页主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>两法差异 (FCFE/FCFF-1)</t>
         </is>
       </c>
-      <c r="D20" s="42">
-        <f>D18/D19-1</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="D22" s="42">
+        <f>D20/D21-1</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Checks页含一致性信息行</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>两法差异原因</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债, FCFE已含净新增借款、直接对应股权; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债/扣少数股东权益, FCFE基于归母净利折现、直接对应归母股权价值, 少数股东权益已在DCF页EV→Equity桥扣除, 本页无需再扣; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④理财净变动(上行勾稽参考行)为现金形态转换, 两法均未计入, 不构成差异来源; ⑤两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B21:J21"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7045,23 +7109,23 @@
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7071,23 +7135,23 @@
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7097,23 +7161,23 @@
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7123,23 +7187,23 @@
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7149,23 +7213,23 @@
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7423,11 +7487,11 @@
         <v>-40</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>C25/DCF!$D$25-1</f>
+        <f>C25/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7436,11 +7500,11 @@
         <v>-20</v>
       </c>
       <c r="C26" s="14">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>C26/DCF!$D$25-1</f>
+        <f>C26/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7449,11 +7513,11 @@
         <v>0</v>
       </c>
       <c r="C27" s="49">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>C27/DCF!$D$25-1</f>
+        <f>C27/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7462,11 +7526,11 @@
         <v>20</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>C28/DCF!$D$25-1</f>
+        <f>C28/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7475,11 +7539,11 @@
         <v>40</v>
       </c>
       <c r="C29" s="14">
-        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>C29/DCF!$D$25-1</f>
+        <f>C29/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7727,7 +7791,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$90)^0.5+F11/(1+Assumptions!$C$90)^1.5+G11/(1+Assumptions!$C$90)^2.5+H11/(1+Assumptions!$C$90)^3.5+I11/(1+Assumptions!$C$90)^4.5+I11*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$90)^0.5+F11/(1+Assumptions!$C$90)^1.5+G11/(1+Assumptions!$C$90)^2.5+H11/(1+Assumptions!$C$90)^3.5+I11/(1+Assumptions!$C$90)^4.5+I11*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7906,7 +7970,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -8092,7 +8156,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$90)^0.5+F30/(1+Assumptions!$C$90)^1.5+G30/(1+Assumptions!$C$90)^2.5+H30/(1+Assumptions!$C$90)^3.5+I30/(1+Assumptions!$C$90)^4.5+I30*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$90)^0.5+F30/(1+Assumptions!$C$90)^1.5+G30/(1+Assumptions!$C$90)^2.5+H30/(1+Assumptions!$C$90)^3.5+I30/(1+Assumptions!$C$90)^4.5+I30*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8543,7 +8607,7 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>DCF!D25&gt;0</f>
+        <f>DCF!D26&gt;0</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -8559,7 +8623,7 @@
         </is>
       </c>
       <c r="B10" s="54">
-        <f>ABS(Sensitivity!E8-DCF!D25)&lt;0.01</f>
+        <f>ABS(Sensitivity!E8-DCF!D26)&lt;0.01</f>
         <v/>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -8782,11 +8846,11 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>FCFE!D18/DCF!D25</f>
+        <f>FCFE!D20/DCF!D26</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -8929,11 +8993,11 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="E5" s="15">
@@ -9094,11 +9158,11 @@
         </is>
       </c>
       <c r="C10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="E10" s="15">

--- a/examples/300476_胜宏科技_估值模型.xlsx
+++ b/examples/300476_胜宏科技_估值模型.xlsx
@@ -1,48 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FIN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
-    <definedName name="WACC_USED">Assumptions!$C$90</definedName>
-    <definedName name="WACC_CALC">Assumptions!$C$88</definedName>
-    <definedName name="TERM_G">Assumptions!$C$91</definedName>
-    <definedName name="KE">Assumptions!$C$86</definedName>
-    <definedName name="KD">Assumptions!$C$87</definedName>
-    <definedName name="RF_RATE">Assumptions!$C$79</definedName>
-    <definedName name="ERP">Assumptions!$C$80</definedName>
-    <definedName name="BETA_U">Assumptions!$C$81</definedName>
+    <definedName name="WACC_USED">Assumptions!$C$91</definedName>
+    <definedName name="WACC_CALC">Assumptions!$C$89</definedName>
+    <definedName name="TERM_G">Assumptions!$C$92</definedName>
+    <definedName name="KE">Assumptions!$C$87</definedName>
+    <definedName name="KD">Assumptions!$C$88</definedName>
+    <definedName name="RF_RATE">Assumptions!$C$80</definedName>
+    <definedName name="ERP">Assumptions!$C$81</definedName>
+    <definedName name="BETA_U">Assumptions!$C$82</definedName>
     <definedName name="TAX_RATE_Y1">Assumptions!$C$41</definedName>
-    <definedName name="PAYOUT_Y1">Assumptions!$C$61</definedName>
-    <definedName name="MIN_CASH_PCT">Assumptions!$C$65</definedName>
+    <definedName name="PAYOUT_Y1">Assumptions!$C$62</definedName>
+    <definedName name="MIN_CASH_PCT">Assumptions!$C$66</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
     <definedName name="DCF_PS">DCF!$D$26</definedName>
     <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -269,8 +269,8 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C20" s="4">
-        <f>TEXT(Assumptions!C88,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C90,"0.00%")</f>
+        <f>TEXT(Assumptions!C89,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C91,"0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1379,23 +1379,23 @@
         </is>
       </c>
       <c r="E13" s="26">
-        <f>IS!E4*Assumptions!$C$65</f>
+        <f>IS!E4*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>IS!F4*Assumptions!$C$65</f>
+        <f>IS!F4*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G13" s="26">
-        <f>IS!G4*Assumptions!$C$65</f>
+        <f>IS!G4*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H13" s="26">
-        <f>IS!H4*Assumptions!$C$65</f>
+        <f>IS!H4*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I13" s="26">
-        <f>IS!I4*Assumptions!$C$65</f>
+        <f>IS!I4*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -1514,23 +1514,23 @@
         </is>
       </c>
       <c r="E19" s="26">
-        <f>Assumptions!C$66</f>
+        <f>Assumptions!C$67</f>
         <v/>
       </c>
       <c r="F19" s="26">
-        <f>Assumptions!D$66</f>
+        <f>Assumptions!D$67</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>Assumptions!E$66</f>
+        <f>Assumptions!E$67</f>
         <v/>
       </c>
       <c r="H19" s="26">
-        <f>Assumptions!F$66</f>
+        <f>Assumptions!F$67</f>
         <v/>
       </c>
       <c r="I19" s="26">
-        <f>Assumptions!G$66</f>
+        <f>Assumptions!G$67</f>
         <v/>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -1742,23 +1742,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>E25*Assumptions!$C$70</f>
+        <f>E25*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>F25*Assumptions!$C$70</f>
+        <f>F25*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>G25*Assumptions!$C$70</f>
+        <f>G25*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>H25*Assumptions!$C$70</f>
+        <f>H25*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>I25*Assumptions!$C$70</f>
+        <f>I25*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -1813,23 +1813,23 @@
         </is>
       </c>
       <c r="E30" s="26">
-        <f>Assumptions!C$67</f>
+        <f>Assumptions!C$68</f>
         <v/>
       </c>
       <c r="F30" s="26">
-        <f>Assumptions!D$67</f>
+        <f>Assumptions!D$68</f>
         <v/>
       </c>
       <c r="G30" s="26">
-        <f>Assumptions!E$67</f>
+        <f>Assumptions!E$68</f>
         <v/>
       </c>
       <c r="H30" s="26">
-        <f>Assumptions!F$67</f>
+        <f>Assumptions!F$68</f>
         <v/>
       </c>
       <c r="I30" s="26">
-        <f>Assumptions!G$67</f>
+        <f>Assumptions!G$68</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -1945,23 +1945,23 @@
         </is>
       </c>
       <c r="E34" s="26">
-        <f>E33*Assumptions!$C$71</f>
+        <f>E33*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="F34" s="26">
-        <f>F33*Assumptions!$C$71</f>
+        <f>F33*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="G34" s="26">
-        <f>G33*Assumptions!$C$71</f>
+        <f>G33*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="H34" s="26">
-        <f>H33*Assumptions!$C$71</f>
+        <f>H33*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="I34" s="26">
-        <f>I33*Assumptions!$C$71</f>
+        <f>I33*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -2016,23 +2016,23 @@
         </is>
       </c>
       <c r="E38" s="26">
-        <f>Assumptions!C$68</f>
+        <f>Assumptions!C$69</f>
         <v/>
       </c>
       <c r="F38" s="26">
-        <f>Assumptions!D$68</f>
+        <f>Assumptions!D$69</f>
         <v/>
       </c>
       <c r="G38" s="26">
-        <f>Assumptions!E$68</f>
+        <f>Assumptions!E$69</f>
         <v/>
       </c>
       <c r="H38" s="26">
-        <f>Assumptions!F$68</f>
+        <f>Assumptions!F$69</f>
         <v/>
       </c>
       <c r="I38" s="26">
-        <f>Assumptions!G$68</f>
+        <f>Assumptions!G$69</f>
         <v/>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -2212,23 +2212,23 @@
         </is>
       </c>
       <c r="E44" s="26">
-        <f>E43*Assumptions!$C$72</f>
+        <f>E43*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="F44" s="26">
-        <f>F43*Assumptions!$C$72</f>
+        <f>F43*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="G44" s="26">
-        <f>G43*Assumptions!$C$72</f>
+        <f>G43*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="H44" s="26">
-        <f>H43*Assumptions!$C$72</f>
+        <f>H43*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="I44" s="26">
-        <f>I43*Assumptions!$C$72</f>
+        <f>I43*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -2283,23 +2283,23 @@
         </is>
       </c>
       <c r="E48" s="26">
-        <f>Assumptions!C$69</f>
+        <f>Assumptions!C$70</f>
         <v/>
       </c>
       <c r="F48" s="26">
-        <f>Assumptions!D$69</f>
+        <f>Assumptions!D$70</f>
         <v/>
       </c>
       <c r="G48" s="26">
-        <f>Assumptions!E$69</f>
+        <f>Assumptions!E$70</f>
         <v/>
       </c>
       <c r="H48" s="26">
-        <f>Assumptions!F$69</f>
+        <f>Assumptions!F$70</f>
         <v/>
       </c>
       <c r="I48" s="26">
-        <f>Assumptions!G$69</f>
+        <f>Assumptions!G$70</f>
         <v/>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -2415,23 +2415,23 @@
         </is>
       </c>
       <c r="E52" s="26">
-        <f>E51*Assumptions!$C$73</f>
+        <f>E51*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F52" s="26">
-        <f>F51*Assumptions!$C$73</f>
+        <f>F51*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G52" s="26">
-        <f>G51*Assumptions!$C$73</f>
+        <f>G51*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H52" s="26">
-        <f>H51*Assumptions!$C$73</f>
+        <f>H51*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I52" s="26">
-        <f>I51*Assumptions!$C$73</f>
+        <f>I51*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -2822,23 +2822,23 @@
         </is>
       </c>
       <c r="E66" s="26">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="F66" s="26">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="H66" s="26">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="I66" s="26">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -2907,23 +2907,23 @@
         </is>
       </c>
       <c r="E72" s="26">
-        <f>E18*Assumptions!$C$70+E29*Assumptions!$C$71+E37*Assumptions!$C$72+E47*Assumptions!$C$73</f>
+        <f>E18*Assumptions!$C$71+E29*Assumptions!$C$72+E37*Assumptions!$C$73+E47*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F72" s="26">
-        <f>F18*Assumptions!$C$70+F29*Assumptions!$C$71+F37*Assumptions!$C$72+F47*Assumptions!$C$73</f>
+        <f>F18*Assumptions!$C$71+F29*Assumptions!$C$72+F37*Assumptions!$C$73+F47*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G72" s="26">
-        <f>G18*Assumptions!$C$70+G29*Assumptions!$C$71+G37*Assumptions!$C$72+G47*Assumptions!$C$73</f>
+        <f>G18*Assumptions!$C$71+G29*Assumptions!$C$72+G37*Assumptions!$C$73+G47*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H72" s="26">
-        <f>H18*Assumptions!$C$70+H29*Assumptions!$C$71+H37*Assumptions!$C$72+H47*Assumptions!$C$73</f>
+        <f>H18*Assumptions!$C$71+H29*Assumptions!$C$72+H37*Assumptions!$C$73+H47*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I72" s="26">
-        <f>I18*Assumptions!$C$70+I29*Assumptions!$C$71+I37*Assumptions!$C$72+I47*Assumptions!$C$73</f>
+        <f>I18*Assumptions!$C$71+I29*Assumptions!$C$72+I37*Assumptions!$C$73+I47*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -2934,23 +2934,23 @@
         </is>
       </c>
       <c r="E73" s="26">
-        <f>E6*Assumptions!$C$74</f>
+        <f>E6*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F73" s="26">
-        <f>F6*Assumptions!$C$74</f>
+        <f>F6*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G73" s="26">
-        <f>G6*Assumptions!$C$74</f>
+        <f>G6*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H73" s="26">
-        <f>H6*Assumptions!$C$74</f>
+        <f>H6*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I73" s="26">
-        <f>I6*Assumptions!$C$74</f>
+        <f>I6*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -2988,23 +2988,23 @@
         </is>
       </c>
       <c r="E75" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$41)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F75" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$41)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G75" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$41)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H75" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$41)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I75" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$41)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -3177,23 +3177,23 @@
         </is>
       </c>
       <c r="E82" s="26">
-        <f>(E18+E80)/2*Assumptions!$C$70+(E29+E32)/2*Assumptions!$C$71+(E37+E81)/2*Assumptions!$C$72+(E47+E50)/2*Assumptions!$C$73</f>
+        <f>(E18+E80)/2*Assumptions!$C$71+(E29+E32)/2*Assumptions!$C$72+(E37+E81)/2*Assumptions!$C$73+(E47+E50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F82" s="26">
-        <f>(F18+F80)/2*Assumptions!$C$70+(F29+F32)/2*Assumptions!$C$71+(F37+F81)/2*Assumptions!$C$72+(F47+F50)/2*Assumptions!$C$73</f>
+        <f>(F18+F80)/2*Assumptions!$C$71+(F29+F32)/2*Assumptions!$C$72+(F37+F81)/2*Assumptions!$C$73+(F47+F50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G82" s="26">
-        <f>(G18+G80)/2*Assumptions!$C$70+(G29+G32)/2*Assumptions!$C$71+(G37+G81)/2*Assumptions!$C$72+(G47+G50)/2*Assumptions!$C$73</f>
+        <f>(G18+G80)/2*Assumptions!$C$71+(G29+G32)/2*Assumptions!$C$72+(G37+G81)/2*Assumptions!$C$73+(G47+G50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H82" s="26">
-        <f>(H18+H80)/2*Assumptions!$C$70+(H29+H32)/2*Assumptions!$C$71+(H37+H81)/2*Assumptions!$C$72+(H47+H50)/2*Assumptions!$C$73</f>
+        <f>(H18+H80)/2*Assumptions!$C$71+(H29+H32)/2*Assumptions!$C$72+(H37+H81)/2*Assumptions!$C$73+(H47+H50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I82" s="26">
-        <f>(I18+I80)/2*Assumptions!$C$70+(I29+I32)/2*Assumptions!$C$71+(I37+I81)/2*Assumptions!$C$72+(I47+I50)/2*Assumptions!$C$73</f>
+        <f>(I18+I80)/2*Assumptions!$C$71+(I29+I32)/2*Assumptions!$C$72+(I37+I81)/2*Assumptions!$C$73+(I47+I50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -3231,23 +3231,23 @@
         </is>
       </c>
       <c r="E84" s="26">
-        <f>(E6+E83)/2*Assumptions!$C$74</f>
+        <f>(E6+E83)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F84" s="26">
-        <f>(F6+F83)/2*Assumptions!$C$74</f>
+        <f>(F6+F83)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G84" s="26">
-        <f>(G6+G83)/2*Assumptions!$C$74</f>
+        <f>(G6+G83)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H84" s="26">
-        <f>(H6+H83)/2*Assumptions!$C$74</f>
+        <f>(H6+H83)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I84" s="26">
-        <f>(I6+I83)/2*Assumptions!$C$74</f>
+        <f>(I6+I83)/2*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -3400,23 +3400,23 @@
         </is>
       </c>
       <c r="E91" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$41)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F91" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$41)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G91" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$41)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H91" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$41)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I91" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$41)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -3589,23 +3589,23 @@
         </is>
       </c>
       <c r="E98" s="26">
-        <f>(E18+E96)/2*Assumptions!$C$70+(E29+E32)/2*Assumptions!$C$71+(E37+E97)/2*Assumptions!$C$72+(E47+E50)/2*Assumptions!$C$73</f>
+        <f>(E18+E96)/2*Assumptions!$C$71+(E29+E32)/2*Assumptions!$C$72+(E37+E97)/2*Assumptions!$C$73+(E47+E50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F98" s="26">
-        <f>(F18+F96)/2*Assumptions!$C$70+(F29+F32)/2*Assumptions!$C$71+(F37+F97)/2*Assumptions!$C$72+(F47+F50)/2*Assumptions!$C$73</f>
+        <f>(F18+F96)/2*Assumptions!$C$71+(F29+F32)/2*Assumptions!$C$72+(F37+F97)/2*Assumptions!$C$73+(F47+F50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G98" s="26">
-        <f>(G18+G96)/2*Assumptions!$C$70+(G29+G32)/2*Assumptions!$C$71+(G37+G97)/2*Assumptions!$C$72+(G47+G50)/2*Assumptions!$C$73</f>
+        <f>(G18+G96)/2*Assumptions!$C$71+(G29+G32)/2*Assumptions!$C$72+(G37+G97)/2*Assumptions!$C$73+(G47+G50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H98" s="26">
-        <f>(H18+H96)/2*Assumptions!$C$70+(H29+H32)/2*Assumptions!$C$71+(H37+H97)/2*Assumptions!$C$72+(H47+H50)/2*Assumptions!$C$73</f>
+        <f>(H18+H96)/2*Assumptions!$C$71+(H29+H32)/2*Assumptions!$C$72+(H37+H97)/2*Assumptions!$C$73+(H47+H50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I98" s="26">
-        <f>(I18+I96)/2*Assumptions!$C$70+(I29+I32)/2*Assumptions!$C$71+(I37+I97)/2*Assumptions!$C$72+(I47+I50)/2*Assumptions!$C$73</f>
+        <f>(I18+I96)/2*Assumptions!$C$71+(I29+I32)/2*Assumptions!$C$72+(I37+I97)/2*Assumptions!$C$73+(I47+I50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -3643,23 +3643,23 @@
         </is>
       </c>
       <c r="E100" s="26">
-        <f>(E6+E99)/2*Assumptions!$C$74</f>
+        <f>(E6+E99)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F100" s="26">
-        <f>(F6+F99)/2*Assumptions!$C$74</f>
+        <f>(F6+F99)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G100" s="26">
-        <f>(G6+G99)/2*Assumptions!$C$74</f>
+        <f>(G6+G99)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H100" s="26">
-        <f>(H6+H99)/2*Assumptions!$C$74</f>
+        <f>(H6+H99)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I100" s="26">
-        <f>(I6+I99)/2*Assumptions!$C$74</f>
+        <f>(I6+I99)/2*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -3812,23 +3812,23 @@
         </is>
       </c>
       <c r="E107" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$41)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F107" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$41)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G107" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$41)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H107" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$41)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I107" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$41)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -4001,23 +4001,23 @@
         </is>
       </c>
       <c r="E114" s="26">
-        <f>(E18+E112)/2*Assumptions!$C$70+(E29+E32)/2*Assumptions!$C$71+(E37+E113)/2*Assumptions!$C$72+(E47+E50)/2*Assumptions!$C$73</f>
+        <f>(E18+E112)/2*Assumptions!$C$71+(E29+E32)/2*Assumptions!$C$72+(E37+E113)/2*Assumptions!$C$73+(E47+E50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F114" s="26">
-        <f>(F18+F112)/2*Assumptions!$C$70+(F29+F32)/2*Assumptions!$C$71+(F37+F113)/2*Assumptions!$C$72+(F47+F50)/2*Assumptions!$C$73</f>
+        <f>(F18+F112)/2*Assumptions!$C$71+(F29+F32)/2*Assumptions!$C$72+(F37+F113)/2*Assumptions!$C$73+(F47+F50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G114" s="26">
-        <f>(G18+G112)/2*Assumptions!$C$70+(G29+G32)/2*Assumptions!$C$71+(G37+G113)/2*Assumptions!$C$72+(G47+G50)/2*Assumptions!$C$73</f>
+        <f>(G18+G112)/2*Assumptions!$C$71+(G29+G32)/2*Assumptions!$C$72+(G37+G113)/2*Assumptions!$C$73+(G47+G50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H114" s="26">
-        <f>(H18+H112)/2*Assumptions!$C$70+(H29+H32)/2*Assumptions!$C$71+(H37+H113)/2*Assumptions!$C$72+(H47+H50)/2*Assumptions!$C$73</f>
+        <f>(H18+H112)/2*Assumptions!$C$71+(H29+H32)/2*Assumptions!$C$72+(H37+H113)/2*Assumptions!$C$73+(H47+H50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I114" s="26">
-        <f>(I18+I112)/2*Assumptions!$C$70+(I29+I32)/2*Assumptions!$C$71+(I37+I113)/2*Assumptions!$C$72+(I47+I50)/2*Assumptions!$C$73</f>
+        <f>(I18+I112)/2*Assumptions!$C$71+(I29+I32)/2*Assumptions!$C$72+(I37+I113)/2*Assumptions!$C$73+(I47+I50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -4055,23 +4055,23 @@
         </is>
       </c>
       <c r="E116" s="26">
-        <f>(E6+E115)/2*Assumptions!$C$74</f>
+        <f>(E6+E115)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F116" s="26">
-        <f>(F6+F115)/2*Assumptions!$C$74</f>
+        <f>(F6+F115)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G116" s="26">
-        <f>(G6+G115)/2*Assumptions!$C$74</f>
+        <f>(G6+G115)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H116" s="26">
-        <f>(H6+H115)/2*Assumptions!$C$74</f>
+        <f>(H6+H115)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I116" s="26">
-        <f>(I6+I115)/2*Assumptions!$C$74</f>
+        <f>(I6+I115)/2*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -4224,23 +4224,23 @@
         </is>
       </c>
       <c r="E123" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$41)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F123" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$41)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G123" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$41)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H123" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$41)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I123" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$41)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -4413,23 +4413,23 @@
         </is>
       </c>
       <c r="E130" s="26">
-        <f>(E18+E128)/2*Assumptions!$C$70+(E29+E32)/2*Assumptions!$C$71+(E37+E129)/2*Assumptions!$C$72+(E47+E50)/2*Assumptions!$C$73</f>
+        <f>(E18+E128)/2*Assumptions!$C$71+(E29+E32)/2*Assumptions!$C$72+(E37+E129)/2*Assumptions!$C$73+(E47+E50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F130" s="26">
-        <f>(F18+F128)/2*Assumptions!$C$70+(F29+F32)/2*Assumptions!$C$71+(F37+F129)/2*Assumptions!$C$72+(F47+F50)/2*Assumptions!$C$73</f>
+        <f>(F18+F128)/2*Assumptions!$C$71+(F29+F32)/2*Assumptions!$C$72+(F37+F129)/2*Assumptions!$C$73+(F47+F50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G130" s="26">
-        <f>(G18+G128)/2*Assumptions!$C$70+(G29+G32)/2*Assumptions!$C$71+(G37+G129)/2*Assumptions!$C$72+(G47+G50)/2*Assumptions!$C$73</f>
+        <f>(G18+G128)/2*Assumptions!$C$71+(G29+G32)/2*Assumptions!$C$72+(G37+G129)/2*Assumptions!$C$73+(G47+G50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H130" s="26">
-        <f>(H18+H128)/2*Assumptions!$C$70+(H29+H32)/2*Assumptions!$C$71+(H37+H129)/2*Assumptions!$C$72+(H47+H50)/2*Assumptions!$C$73</f>
+        <f>(H18+H128)/2*Assumptions!$C$71+(H29+H32)/2*Assumptions!$C$72+(H37+H129)/2*Assumptions!$C$73+(H47+H50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I130" s="26">
-        <f>(I18+I128)/2*Assumptions!$C$70+(I29+I32)/2*Assumptions!$C$71+(I37+I129)/2*Assumptions!$C$72+(I47+I50)/2*Assumptions!$C$73</f>
+        <f>(I18+I128)/2*Assumptions!$C$71+(I29+I32)/2*Assumptions!$C$72+(I37+I129)/2*Assumptions!$C$73+(I47+I50)/2*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -4467,23 +4467,23 @@
         </is>
       </c>
       <c r="E132" s="26">
-        <f>(E6+E131)/2*Assumptions!$C$74</f>
+        <f>(E6+E131)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F132" s="26">
-        <f>(F6+F131)/2*Assumptions!$C$74</f>
+        <f>(F6+F131)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G132" s="26">
-        <f>(G6+G131)/2*Assumptions!$C$74</f>
+        <f>(G6+G131)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H132" s="26">
-        <f>(H6+H131)/2*Assumptions!$C$74</f>
+        <f>(H6+H131)/2*Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I132" s="26">
-        <f>(I6+I131)/2*Assumptions!$C$74</f>
+        <f>(I6+I131)/2*Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -4587,23 +4587,23 @@
         </is>
       </c>
       <c r="E138" s="39">
-        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$74)</f>
+        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="F138" s="39">
-        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$74)</f>
+        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="G138" s="39">
-        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$74)</f>
+        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="H138" s="39">
-        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$74)</f>
+        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="I138" s="39">
-        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$74)</f>
+        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="J138" s="11" t="inlineStr">
@@ -4952,23 +4952,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>IS!E20*Assumptions!$C$62</f>
+        <f>IS!E20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>IS!F20*Assumptions!$C$62</f>
+        <f>IS!F20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>IS!G20*Assumptions!$C$62</f>
+        <f>IS!G20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>IS!H20*Assumptions!$C$62</f>
+        <f>IS!H20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>IS!I20*Assumptions!$C$62</f>
+        <f>IS!I20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -5293,7 +5293,7 @@
           <t>稀释后股数(百万股)</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>C19+C20</f>
         <v/>
       </c>
@@ -5392,23 +5392,23 @@
         </is>
       </c>
       <c r="E4" s="26">
-        <f>IS!E23</f>
+        <f>IS!E24</f>
         <v/>
       </c>
       <c r="F4" s="26">
-        <f>IS!F23</f>
+        <f>IS!F24</f>
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>IS!G23</f>
+        <f>IS!G24</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>IS!H23</f>
+        <f>IS!H24</f>
         <v/>
       </c>
       <c r="I4" s="26">
-        <f>IS!I23</f>
+        <f>IS!I24</f>
         <v/>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -5623,23 +5623,23 @@
         </is>
       </c>
       <c r="E12" s="31">
-        <f>1/(1+Assumptions!$C$90)^E11</f>
+        <f>1/(1+Assumptions!$C$91)^E11</f>
         <v/>
       </c>
       <c r="F12" s="31">
-        <f>1/(1+Assumptions!$C$90)^F11</f>
+        <f>1/(1+Assumptions!$C$91)^F11</f>
         <v/>
       </c>
       <c r="G12" s="31">
-        <f>1/(1+Assumptions!$C$90)^G11</f>
+        <f>1/(1+Assumptions!$C$91)^G11</f>
         <v/>
       </c>
       <c r="H12" s="31">
-        <f>1/(1+Assumptions!$C$90)^H11</f>
+        <f>1/(1+Assumptions!$C$91)^H11</f>
         <v/>
       </c>
       <c r="I12" s="31">
-        <f>1/(1+Assumptions!$C$90)^I11</f>
+        <f>1/(1+Assumptions!$C$91)^I11</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)</f>
+        <f>I10*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D30" s="43">
-        <f>D18/(IS!E23+PPE!E19)</f>
+        <f>D18/(IS!E24+PPE!E19)</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
+          <t>单位: 人民币百万元 | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按D×g稳态正常化)</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <f>I10-I8+FIN!I56*TERM_G</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+          <t>终值净借款按D×g稳态正常化: 终值年净新增借款=2030E期末有息负债×g(替代实际调度值, 对称防止显性期末大额净融资/净偿还被Gordon公式永续外推)</t>
         </is>
       </c>
     </row>
@@ -7083,29 +7083,29 @@
         </is>
       </c>
       <c r="C5" s="42">
-        <f>Assumptions!$C$91-0.0100</f>
+        <f>Assumptions!$C$92-0.0100</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>Assumptions!$C$91-0.0050</f>
+        <f>Assumptions!$C$92-0.0050</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="F5" s="42">
-        <f>Assumptions!$C$91+0.0050</f>
+        <f>Assumptions!$C$92+0.0050</f>
         <v/>
       </c>
       <c r="G5" s="42">
-        <f>Assumptions!$C$91+0.0100</f>
+        <f>Assumptions!$C$92+0.0100</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="42">
-        <f>Assumptions!$C$90-0.0100</f>
+        <f>Assumptions!$C$91-0.0100</f>
         <v/>
       </c>
       <c r="C6" s="14">
@@ -7131,7 +7131,7 @@
     </row>
     <row r="7">
       <c r="B7" s="42">
-        <f>Assumptions!$C$90-0.0050</f>
+        <f>Assumptions!$C$91-0.0050</f>
         <v/>
       </c>
       <c r="C7" s="14">
@@ -7157,7 +7157,7 @@
     </row>
     <row r="8">
       <c r="B8" s="42">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="C8" s="14">
@@ -7183,7 +7183,7 @@
     </row>
     <row r="9">
       <c r="B9" s="42">
-        <f>Assumptions!$C$90+0.0050</f>
+        <f>Assumptions!$C$91+0.0050</f>
         <v/>
       </c>
       <c r="C9" s="14">
@@ -7209,7 +7209,7 @@
     </row>
     <row r="10">
       <c r="B10" s="42">
-        <f>Assumptions!$C$90+0.0100</f>
+        <f>Assumptions!$C$91+0.0100</f>
         <v/>
       </c>
       <c r="C10" s="14">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
+          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 首年按全额COGS重定价, 以后年按ΔCOGS; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
         <v>-40</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
@@ -7500,7 +7500,7 @@
         <v>-20</v>
       </c>
       <c r="C26" s="14">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="49">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
@@ -7526,7 +7526,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
@@ -7539,7 +7539,7 @@
         <v>40</v>
       </c>
       <c r="C29" s="14">
-        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$90)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$90)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$90)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$90)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$90)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B29/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D29" s="16">
@@ -7550,7 +7550,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>DPO每±20天≈FCFF±(Δ营业成本×20/365); 基准DPO路径见Assumptions(300→260天)</t>
+          <t>DPO每±20天: 首年≈FCFF±(营业成本×20/365), 以后年≈±(Δ营业成本×20/365); 基准DPO路径见Assumptions(300→260天)</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第95行</t>
+          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第96行</t>
         </is>
       </c>
     </row>
@@ -7683,23 +7683,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$95)</f>
+        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>E8*(1+Revenue_Segments!F39+Assumptions!$C$95)</f>
+        <f>E8*(1+Revenue_Segments!F39+Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>F8*(1+Revenue_Segments!G39+Assumptions!$C$95)</f>
+        <f>F8*(1+Revenue_Segments!G39+Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>G8*(1+Revenue_Segments!H39+Assumptions!$C$95)</f>
+        <f>G8*(1+Revenue_Segments!H39+Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>H8*(1+Revenue_Segments!I39+Assumptions!$C$95)</f>
+        <f>H8*(1+Revenue_Segments!I39+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -7710,23 +7710,23 @@
         </is>
       </c>
       <c r="E9" s="16">
-        <f>(Revenue_Segments!E40+Assumptions!$D$95-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$42)*(1-Assumptions!C$41)</f>
+        <f>(Revenue_Segments!E40+Assumptions!$D$96-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$43)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(Revenue_Segments!F40+Assumptions!$D$95-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$42)*(1-Assumptions!D$41)</f>
+        <f>(Revenue_Segments!F40+Assumptions!$D$96-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$43)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(Revenue_Segments!G40+Assumptions!$D$95-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$42)*(1-Assumptions!E$41)</f>
+        <f>(Revenue_Segments!G40+Assumptions!$D$96-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$43)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(Revenue_Segments!H40+Assumptions!$D$95-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$42)*(1-Assumptions!F$41)</f>
+        <f>(Revenue_Segments!H40+Assumptions!$D$96-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$43)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>(Revenue_Segments!I40+Assumptions!$D$95-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$42)*(1-Assumptions!G$41)</f>
+        <f>(Revenue_Segments!I40+Assumptions!$D$96-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$43)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$90)^0.5+F11/(1+Assumptions!$C$90)^1.5+G11/(1+Assumptions!$C$90)^2.5+H11/(1+Assumptions!$C$90)^3.5+I11/(1+Assumptions!$C$90)^4.5+I11*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$91)^0.5+F11/(1+Assumptions!$C$91)^1.5+G11/(1+Assumptions!$C$91)^2.5+H11/(1+Assumptions!$C$91)^3.5+I11/(1+Assumptions!$C$91)^4.5+I11*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第96行</t>
+          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第97行</t>
         </is>
       </c>
     </row>
@@ -7862,23 +7862,23 @@
         </is>
       </c>
       <c r="E17" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$96)</f>
+        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="F17" s="26">
-        <f>E17*(1+Revenue_Segments!F39+Assumptions!$C$96)</f>
+        <f>E17*(1+Revenue_Segments!F39+Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="G17" s="26">
-        <f>F17*(1+Revenue_Segments!G39+Assumptions!$C$96)</f>
+        <f>F17*(1+Revenue_Segments!G39+Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="H17" s="26">
-        <f>G17*(1+Revenue_Segments!H39+Assumptions!$C$96)</f>
+        <f>G17*(1+Revenue_Segments!H39+Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="I17" s="26">
-        <f>H17*(1+Revenue_Segments!I39+Assumptions!$C$96)</f>
+        <f>H17*(1+Revenue_Segments!I39+Assumptions!$C$97)</f>
         <v/>
       </c>
     </row>
@@ -7889,23 +7889,23 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>(Revenue_Segments!E40+Assumptions!$D$96-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$42)*(1-Assumptions!C$41)</f>
+        <f>(Revenue_Segments!E40+Assumptions!$D$97-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$43)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>(Revenue_Segments!F40+Assumptions!$D$96-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$42)*(1-Assumptions!D$41)</f>
+        <f>(Revenue_Segments!F40+Assumptions!$D$97-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$43)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>(Revenue_Segments!G40+Assumptions!$D$96-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$42)*(1-Assumptions!E$41)</f>
+        <f>(Revenue_Segments!G40+Assumptions!$D$97-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$43)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>(Revenue_Segments!H40+Assumptions!$D$96-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$42)*(1-Assumptions!F$41)</f>
+        <f>(Revenue_Segments!H40+Assumptions!$D$97-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$43)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>(Revenue_Segments!I40+Assumptions!$D$96-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$42)*(1-Assumptions!G$41)</f>
+        <f>(Revenue_Segments!I40+Assumptions!$D$97-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$43)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第97行</t>
+          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第98行</t>
         </is>
       </c>
     </row>
@@ -8048,23 +8048,23 @@
         </is>
       </c>
       <c r="E27" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$97)</f>
+        <f>IS!D4*(1+Revenue_Segments!E39+Assumptions!$C$98)</f>
         <v/>
       </c>
       <c r="F27" s="26">
-        <f>E27*(1+Revenue_Segments!F39+Assumptions!$C$97)</f>
+        <f>E27*(1+Revenue_Segments!F39+Assumptions!$C$98)</f>
         <v/>
       </c>
       <c r="G27" s="26">
-        <f>F27*(1+Revenue_Segments!G39+Assumptions!$C$97)</f>
+        <f>F27*(1+Revenue_Segments!G39+Assumptions!$C$98)</f>
         <v/>
       </c>
       <c r="H27" s="26">
-        <f>G27*(1+Revenue_Segments!H39+Assumptions!$C$97)</f>
+        <f>G27*(1+Revenue_Segments!H39+Assumptions!$C$98)</f>
         <v/>
       </c>
       <c r="I27" s="26">
-        <f>H27*(1+Revenue_Segments!I39+Assumptions!$C$97)</f>
+        <f>H27*(1+Revenue_Segments!I39+Assumptions!$C$98)</f>
         <v/>
       </c>
     </row>
@@ -8075,23 +8075,23 @@
         </is>
       </c>
       <c r="E28" s="16">
-        <f>(Revenue_Segments!E40+Assumptions!$D$97-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$42)*(1-Assumptions!C$41)</f>
+        <f>(Revenue_Segments!E40+Assumptions!$D$98-Assumptions!C$35-Assumptions!C$36-Assumptions!C$37-Assumptions!C$38-Assumptions!$C$43)*(1-Assumptions!C$41)*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>(Revenue_Segments!F40+Assumptions!$D$97-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$42)*(1-Assumptions!D$41)</f>
+        <f>(Revenue_Segments!F40+Assumptions!$D$98-Assumptions!D$35-Assumptions!D$36-Assumptions!D$37-Assumptions!D$38-Assumptions!$C$43)*(1-Assumptions!D$41)*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>(Revenue_Segments!G40+Assumptions!$D$97-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$42)*(1-Assumptions!E$41)</f>
+        <f>(Revenue_Segments!G40+Assumptions!$D$98-Assumptions!E$35-Assumptions!E$36-Assumptions!E$37-Assumptions!E$38-Assumptions!$C$43)*(1-Assumptions!E$41)*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>(Revenue_Segments!H40+Assumptions!$D$97-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$42)*(1-Assumptions!F$41)</f>
+        <f>(Revenue_Segments!H40+Assumptions!$D$98-Assumptions!F$35-Assumptions!F$36-Assumptions!F$37-Assumptions!F$38-Assumptions!$C$43)*(1-Assumptions!F$41)*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>(Revenue_Segments!I40+Assumptions!$D$97-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$42)*(1-Assumptions!G$41)</f>
+        <f>(Revenue_Segments!I40+Assumptions!$D$98-Assumptions!G$35-Assumptions!G$36-Assumptions!G$37-Assumptions!G$38-Assumptions!$C$43)*(1-Assumptions!G$41)*(1-Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$90)^0.5+F30/(1+Assumptions!$C$90)^1.5+G30/(1+Assumptions!$C$90)^2.5+H30/(1+Assumptions!$C$90)^3.5+I30/(1+Assumptions!$C$90)^4.5+I30*(1+Assumptions!$C$91)/(Assumptions!$C$90-Assumptions!$C$91)/(1+Assumptions!$C$90)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$91)^0.5+F30/(1+Assumptions!$C$91)^1.5+G30/(1+Assumptions!$C$91)^2.5+H30/(1+Assumptions!$C$91)^3.5+I30/(1+Assumptions!$C$91)^4.5+I30*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. 毛利率处于(0,60%)合理区间</t>
+          <t>5. 信息项(不闸门): 毛利率处于(0%,60%)区间</t>
         </is>
       </c>
       <c r="B8" s="54">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>防止假设越界</t>
+          <t>信息行, 不参与布尔汇总; 越界仅提示复核毛利率假设; 区间可经checks.gm_band配置</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>OR(ABS(Assumptions!C90-Assumptions!C88)&lt;0.000001,Assumptions!C89&lt;&gt;"")</f>
+        <f>OR(ABS(Assumptions!C91-Assumptions!C89)&lt;0.000001,Assumptions!C90&lt;&gt;"")</f>
         <v/>
       </c>
       <c r="J11" s="11" t="inlineStr">
@@ -8826,11 +8826,11 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>Assumptions!C88</f>
+        <f>Assumptions!C89</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>Assumptions!C90</f>
+        <f>Assumptions!C91</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="F24" s="57">
-        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
+        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
         <v/>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="F25" s="27">
-        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
+        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
         <v/>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10186,66 +10186,66 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>少数股东损益占净利润比</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>按历史均值自动推导: (合并净利-归母)/合并净利 3年均值+0.00%, clamp[0,50%]→采用0.00%; config可经model.mi_share覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>其他及财务费用率合计(情景页用)</t>
         </is>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C42" s="28" t="n">
+      <c r="C43" s="28" t="n">
         <v>0.006</v>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>财务费用率(2025A 0.62%)+其他经营损益+营业外净额近似, 供Scenarios页简化净利率计算</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>六、营运资本天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>DSO 应收(票据+账款)天数</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="C45" s="30" t="n">
-        <v>112</v>
-      </c>
-      <c r="D45" s="30" t="n">
-        <v>110</v>
-      </c>
-      <c r="E45" s="30" t="n">
-        <v>108</v>
-      </c>
-      <c r="F45" s="30" t="n">
-        <v>106</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>105</v>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>2025A 114.7天(2024A 138.7天); 大客户账期稳定, 小幅改善</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>DIO 存货天数</t>
+          <t>DSO 应收(票据+账款)天数</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
@@ -10254,30 +10254,30 @@
         </is>
       </c>
       <c r="C46" s="30" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D46" s="30" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E46" s="30" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F46" s="30" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G46" s="30" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>2025A 92.3天(2024A 90.0天); 备料随AI订单增长, 周转基本持平</t>
+          <t>2025A 114.7天(2024A 138.7天); 大客户账期稳定, 小幅改善</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>DPO 应付(票据+账款)天数</t>
+          <t>DIO 存货天数</t>
         </is>
       </c>
       <c r="B47" s="21" t="inlineStr">
@@ -10286,62 +10286,62 @@
         </is>
       </c>
       <c r="C47" s="30" t="n">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="D47" s="30" t="n">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="E47" s="30" t="n">
-        <v>280</v>
+        <v>88</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>2025A 307.4天(2024A 218.4天); 票据结算占比高+对上游议价力强, 假设逐步回归; Sensitivity页有DPO单维敏感性</t>
+          <t>2025A 92.3天(2024A 90.0天); 备料随AI订单增长, 周转基本持平</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>预付款项/收入</t>
+          <t>DPO 应付(票据+账款)天数</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D48" s="28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E48" s="28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G48" s="28" t="n">
-        <v>0.004</v>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>290</v>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>280</v>
+      </c>
+      <c r="F48" s="30" t="n">
+        <v>270</v>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>260</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>2025A 0.41%</t>
+          <t>2025A 307.4天(2024A 218.4天); 票据结算占比高+对上游议价力强, 假设逐步回归; Sensitivity页有DPO单维敏感性</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>应付职工薪酬/收入</t>
+          <t>预付款项/收入</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
@@ -10350,101 +10350,101 @@
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="D49" s="28" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="E49" s="28" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="G49" s="28" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>2025A 1.45%</t>
+          <t>2025A 0.41%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>应付职工薪酬/收入</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>2025A 1.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>应交税费/收入</t>
         </is>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C50" s="28" t="n">
+      <c r="C51" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="D50" s="28" t="n">
+      <c r="D51" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="E50" s="28" t="n">
+      <c r="E51" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="F51" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="G50" s="28" t="n">
+      <c r="G51" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>2025A 2.44%, 盈利大增后回归</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>七、资本开支与折旧摊销 (PP&amp;E页驱动)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Capex占收入比</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C53" s="28" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D53" s="28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E53" s="28" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F53" s="28" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G53" s="28" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>2025A 34.3%(66.2亿), 2026Q1单季35.7亿; 惠州厂房四爬坡/九封顶/十&amp;十一在建+泰国A1/A2+越南, 媒体口径约200亿投资计划, 逐年退坡</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>在建工程转固率</t>
+          <t>Capex占收入比</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
@@ -10453,18 +10453,30 @@
         </is>
       </c>
       <c r="C54" s="28" t="n">
-        <v>0.75</v>
+        <v>0.28</v>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G54" s="28" t="n">
+        <v>0.09</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>当年转固=(期初在建+当年Capex)×75%; 惠州/泰国项目建设期1-2年, 转固滞后于资本开支</t>
+          <t>2025A 34.3%(66.2亿), 2026Q1单季35.7亿; 惠州厂房四爬坡/九封顶/十&amp;十一在建+泰国A1/A2+越南, 媒体口径约200亿投资计划, 逐年退坡</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>固定资产折旧率(期初净值)</t>
+          <t>在建工程转固率</t>
         </is>
       </c>
       <c r="B55" s="21" t="inlineStr">
@@ -10473,18 +10485,18 @@
         </is>
       </c>
       <c r="C55" s="28" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>2025A折旧摊销9.9亿/期初(固资+在建)74.3亿≈13.4%(含在建口径), 固定资产净值口径取12%; 隐含年限见PP&amp;E页校验行</t>
+          <t>当年转固=(期初在建+当年Capex)×75%; 惠州/泰国项目建设期1-2年, 转固滞后于资本开支</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>当年转固部分折旧率</t>
+          <t>固定资产折旧率(期初净值)</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
@@ -10493,18 +10505,18 @@
         </is>
       </c>
       <c r="C56" s="28" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>转固按约半年投产计提</t>
+          <t>2025A折旧摊销9.9亿/期初(固资+在建)74.3亿≈13.4%(含在建口径), 固定资产净值口径取12%; 隐含年限见PP&amp;E页校验行</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>固定资产处置率(期初净值)</t>
+          <t>当年转固部分折旧率</t>
         </is>
       </c>
       <c r="B57" s="21" t="inlineStr">
@@ -10513,156 +10525,144 @@
         </is>
       </c>
       <c r="C57" s="28" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>设备更新处置, 小额</t>
+          <t>转固按约半年投产计提</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>固定资产处置率(期初净值)</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>设备更新处置, 小额</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>无形资产摊销率(期初)</t>
         </is>
       </c>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C58" s="28" t="n">
+      <c r="C59" s="28" t="n">
         <v>0.08</v>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>2025A无形摊销0.49亿/期初7.56亿≈6.5%, 取8%</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>八、股利与盈余公积</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>股利支付率(按上年归母)</t>
-        </is>
-      </c>
-      <c r="B61" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C61" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D61" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E61" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F61" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G61" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>2025年实付3.8亿≈2024归母的33%; 假设30%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>股利支付率(按上年归母)</t>
+        </is>
+      </c>
+      <c r="B62" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D62" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E62" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F62" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G62" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>2025年实付3.8亿≈2024归母的33%; 假设30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
           <t>法定盈余公积计提率(按当年归母)</t>
         </is>
       </c>
-      <c r="B62" s="21" t="inlineStr">
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C62" s="28" t="n">
+      <c r="C63" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>公司法定盈余公积按净利润10%计提(计至股本50%为止, 本模型从简不提终止); 见Equity_Roll页</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>九、债务与融资 (FIN页调度输入)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>最低现金占收入比</t>
-        </is>
-      </c>
-      <c r="B65" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C65" s="28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>经营性最低货币资金=收入×2%(约7.3天收入, 覆盖付现成本零头); 超出部分由FIN页sweep还债/购买理财</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>短期借款(revolver)计划还款</t>
+          <t>最低现金占收入比</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="29" t="n">
-        <v>0</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="n">
+        <v>0.02</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>revolver属性: 无计划还款, 由资金缺口新增/现金sweep调节; 2025A末15.0亿</t>
+          <t>经营性最低货币资金=收入×2%(约7.3天收入, 覆盖付现成本零头); 超出部分由FIN页sweep还债/购买理财</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债计划还款</t>
+          <t>短期借款(revolver)计划还款</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
@@ -10671,30 +10671,30 @@
         </is>
       </c>
       <c r="C67" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D67" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E67" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F67" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G67" s="29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>2025A末9.96亿, 假设每年偿付3亿至清零</t>
+          <t>revolver属性: 无计划还款, 由资金缺口新增/现金sweep调节; 2025A末15.0亿</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>长期借款计划还款</t>
+          <t>一年内到期非流动负债计划还款</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
@@ -10703,30 +10703,30 @@
         </is>
       </c>
       <c r="C68" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D68" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E68" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F68" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G68" s="29" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>2025A末38.7亿(扩产项目贷), 计划还款5亿/年+现金sweep提前偿还</t>
+          <t>2025A末9.96亿, 假设每年偿付3亿至清零</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>租赁负债计划还款</t>
+          <t>长期借款计划还款</t>
         </is>
       </c>
       <c r="B69" s="21" t="inlineStr">
@@ -10735,50 +10735,62 @@
         </is>
       </c>
       <c r="C69" s="29" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="D69" s="29" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="E69" s="29" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="F69" s="29" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="G69" s="29" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>2025A末0.82亿, 小额摊还</t>
+          <t>2025A末38.7亿(扩产项目贷), 计划还款5亿/年+现金sweep提前偿还</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>短期借款利率</t>
+          <t>租赁负债计划还款</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="n">
-        <v>0.03</v>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>一年期LPR附近(2026-08: 3.0%)</t>
+          <t>2025A末0.82亿, 小额摊还</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债利率</t>
+          <t>短期借款利率</t>
         </is>
       </c>
       <c r="B71" s="21" t="inlineStr">
@@ -10787,18 +10799,18 @@
         </is>
       </c>
       <c r="C71" s="28" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>参照历史综合借款成本</t>
+          <t>一年期LPR附近(2026-08: 3.0%)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>长期借款利率</t>
+          <t>一年内到期非流动负债利率</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
@@ -10807,18 +10819,18 @@
         </is>
       </c>
       <c r="C72" s="28" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>项目贷/海外贷略高</t>
+          <t>参照历史综合借款成本</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>租赁负债利率</t>
+          <t>长期借款利率</t>
         </is>
       </c>
       <c r="B73" s="21" t="inlineStr">
@@ -10827,18 +10839,18 @@
         </is>
       </c>
       <c r="C73" s="28" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>租赁内含利率惯例4-5%</t>
+          <t>项目贷/海外贷略高</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>货币资金收益率(按平均余额)</t>
+          <t>租赁负债利率</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
@@ -10847,85 +10859,85 @@
         </is>
       </c>
       <c r="C74" s="28" t="n">
-        <v>0.012</v>
+        <v>0.045</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>活期+短期存款; 理财收益从简不计(保守)</t>
+          <t>租赁内含利率惯例4-5%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>其他财务费用(手续费/汇兑)</t>
+          <t>货币资金收益率(按平均余额)</t>
         </is>
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="n">
-        <v>30</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="n">
+        <v>0.012</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>历史小额, 取30百万</t>
+          <t>活期+短期存款; 理财收益从简不计(保守)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>其他财务费用(手续费/汇兑)</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="inlineStr">
+        <is>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>历史小额, 取30百万</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>2025A末有息负债合计</t>
         </is>
       </c>
-      <c r="B76" s="21" t="inlineStr">
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>百万</t>
         </is>
       </c>
-      <c r="C76" s="25" t="n">
+      <c r="C77" s="25" t="n">
         <v>6445.6</v>
       </c>
-      <c r="H76" s="11" t="inlineStr">
+      <c r="H77" s="11" t="inlineStr">
         <is>
           <t>＝短借1499.7+一年内996.2+长借3867.4+租赁82.3 (东财F10 2025年报); WACC的Wd市值口径引用本行</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>十、WACC 与终值 (全公式化, 联动Relative_Val可比beta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>无风险利率 rf</t>
-        </is>
-      </c>
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C79" s="28" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>10年期国债收益率约2.0%(2026-08)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>股权风险溢价 ERP</t>
+          <t>无风险利率 rf</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
@@ -10934,81 +10946,80 @@
         </is>
       </c>
       <c r="C80" s="28" t="n">
-        <v>0.055</v>
+        <v>0.02</v>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>A股ERP中枢5.5%</t>
+          <t>10年期国债收益率约2.0%(2026-08)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>可比公司无杠杆βu中位数</t>
+          <t>股权风险溢价 ERP</t>
         </is>
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C81" s="31">
-        <f>Relative_Val!$O$10</f>
-        <v/>
-      </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>＝MEDIAN(可比公司βl/(1+(1-t)×D/E)), 见Relative_Val页L-O列; 改可比beta输入即联动</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>A股ERP中枢5.5%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>目标债务权重 Wd (市值口径)</t>
+          <t>可比公司无杠杆βu中位数</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C82" s="16">
-        <f>C76/(C76+C9)</f>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C82" s="31">
+        <f>Relative_Val!$O$10</f>
         <v/>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>＝2025A末有息负债/(有息负债+总市值): 公司低杠杆+净现金, 以市值口径现状结构为目标结构(书面依据: 公司无有息负债目标指引, 历史D/(D+E) 2-8%, 取现状≈2.4%而非行业15%以避免高估税盾)</t>
+          <t>＝MEDIAN(可比公司βl/(1+(1-t)×D/E)), 见Relative_Val页L-O列; 改可比beta输入即联动</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>目标 D/E = Wd/(1-Wd)</t>
+          <t>目标债务权重 Wd (市值口径)</t>
         </is>
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C83" s="31">
-        <f>C82/(1-C82)</f>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C83" s="16">
+        <f>C77/(C77+C9)</f>
         <v/>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>relever用目标产权比率</t>
+          <t>＝2025A末有息负债/(有息负债+总市值): 公司低杠杆+净现金, 以市值口径现状结构为目标结构(书面依据: 公司无有息负债目标指引, 历史D/(D+E) 2-8%, 取现状≈2.4%而非行业15%以避免高估税盾)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
+          <t>目标 D/E = Wd/(1-Wd)</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
@@ -11017,39 +11028,40 @@
         </is>
       </c>
       <c r="C84" s="31">
-        <f>C81*(1+(1-C41)*C83)</f>
+        <f>C83/(1-C83)</f>
         <v/>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Hamada公式, t=2026E有效税率</t>
+          <t>relever用目标产权比率</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>个股/执行风险溢价 (已删除=0)</t>
+          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
         </is>
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C85" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>原1.6%溢价已删除, 量化依据: 无法从公开数据分离个股特异溢价, 且执行风险已由relevered β(可比含产能爬坡标的)与情景分析(熊市-15pct增速)双重覆盖, 保留会造成重复计价; 如需可自行输入</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C85" s="31">
+        <f>C82*(1+(1-C41)*C84)</f>
+        <v/>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>Hamada公式, t=2026E有效税率</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
+          <t>个股/执行风险溢价 (已删除=0)</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -11057,20 +11069,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C86" s="16">
-        <f>C79+C84*C80+C85</f>
-        <v/>
-      </c>
-      <c r="H86" s="11" t="inlineStr">
-        <is>
-          <t>CAPM公式(溢价默认为0)</t>
+      <c r="C86" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>原1.6%溢价已删除, 量化依据: 无法从公开数据分离个股特异溢价, 且执行风险已由relevered β(可比含产能爬坡标的)与情景分析(熊市-15pct增速)双重覆盖, 保留会造成重复计价; 如需可自行输入</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>债务成本 Kd</t>
+          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
         </is>
       </c>
       <c r="B87" s="21" t="inlineStr">
@@ -11078,19 +11089,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C87" s="28" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>≈FIN页四档债务加权平均利率</t>
+      <c r="C87" s="16">
+        <f>C80+C85*C81+C86</f>
+        <v/>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>CAPM公式(溢价默认为0)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>WACC (计算值)</t>
+          <t>债务成本 Kd</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
@@ -11098,20 +11110,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C88" s="16">
-        <f>(1-C82)*C86+C82*C87*(1-C41)</f>
-        <v/>
-      </c>
-      <c r="H88" s="11" t="inlineStr">
-        <is>
-          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
+      <c r="C88" s="28" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>≈FIN页四档债务加权平均利率</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>WACC override (留空=用计算值)</t>
+          <t>WACC (计算值)</t>
         </is>
       </c>
       <c r="B89" s="21" t="inlineStr">
@@ -11119,17 +11130,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C89" s="28" t="n"/>
+      <c r="C89" s="16">
+        <f>(1-C83)*C87+C83*C88*(1-C41)</f>
+        <v/>
+      </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
+          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>WACC (采用值)</t>
+          <t>WACC override (留空=用计算值)</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
@@ -11137,114 +11151,132 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C90" s="18">
-        <f>IF(C89="",C88,C89)</f>
-        <v/>
-      </c>
+      <c r="C90" s="28" t="n"/>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>WACC (采用值)</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C91" s="18">
+        <f>IF(C90="",C89,C90)</f>
+        <v/>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
           <t>永续增长率 g</t>
         </is>
       </c>
-      <c r="B91" s="21" t="inlineStr">
+      <c r="B92" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C91" s="28" t="n">
+      <c r="C92" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="H92" s="9" t="inlineStr">
         <is>
           <t>长期名义增速中枢下沿; Sensitivity页做敏感分析</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="19" t="inlineStr">
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="19" t="inlineStr">
         <is>
           <t>十一、情景参数 (驱动情景开关 &amp; Scenarios页)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>情景</t>
         </is>
       </c>
-      <c r="C94" s="27" t="inlineStr">
+      <c r="C95" s="27" t="inlineStr">
         <is>
           <t>收入增速调整</t>
         </is>
       </c>
-      <c r="D94" s="27" t="inlineStr">
+      <c r="D95" s="27" t="inlineStr">
         <is>
           <t>净利率调整</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>情景逻辑</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="32" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="32" t="inlineStr">
         <is>
           <t>熊市 Bear</t>
         </is>
       </c>
-      <c r="C95" s="28" t="n">
+      <c r="C96" s="28" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D95" s="28" t="n">
+      <c r="D96" s="28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="H96" s="11" t="inlineStr">
         <is>
           <t>AI capex下修/大客户份额流失/CCL涨价无法顺价; 分部增速-15pct, 净利率-3pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>基准 Base</t>
-        </is>
-      </c>
-      <c r="C96" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="11" t="inlineStr">
-        <is>
-          <t>2026E营收+71.8%≈一致预期(+73%), 2027-28E略低于一致预期; 净利率25-26%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
+          <t>基准 Base</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>2026E营收+71.8%≈一致预期(+73%), 2027-28E略低于一致预期; 净利率25-26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
           <t>牛市 Bull</t>
         </is>
       </c>
-      <c r="C97" s="28" t="n">
+      <c r="C98" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="D97" s="28" t="n">
+      <c r="D98" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="H97" s="11" t="inlineStr">
+      <c r="H98" s="11" t="inlineStr">
         <is>
           <t>TPU/GPU订单超预期+泰国/惠州新产能满销+涨价弹性; 分部增速+10pct, 净利率+1.5pct</t>
         </is>
@@ -11252,18 +11284,18 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A64:J64"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A93:J93"/>
-    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A94:J94"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A61:J61"/>
     <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A65:J65"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A60:J60"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11487,23 +11519,23 @@
         </is>
       </c>
       <c r="E8" s="16">
-        <f>(Assumptions!C$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!C$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(Assumptions!D$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!D$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>(Assumptions!E$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!E$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>(Assumptions!F$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!F$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -11570,23 +11602,23 @@
         <v>0.435</v>
       </c>
       <c r="E10" s="16">
-        <f>(Assumptions!C$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!C$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>(Assumptions!D$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!D$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>(Assumptions!E$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!E$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>(Assumptions!F$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!F$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>(Assumptions!G$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!G$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -11750,23 +11782,23 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>(Assumptions!C$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!C$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>(Assumptions!D$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!D$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>(Assumptions!E$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!E$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>(Assumptions!F$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!F$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>(Assumptions!G$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!G$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -11833,23 +11865,23 @@
         <v>0.244</v>
       </c>
       <c r="E18" s="16">
-        <f>(Assumptions!C$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!C$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>(Assumptions!D$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!D$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>(Assumptions!E$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!E$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>(Assumptions!F$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!F$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>(Assumptions!G$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!G$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -12013,23 +12045,23 @@
         </is>
       </c>
       <c r="E24" s="16">
-        <f>(Assumptions!C$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!C$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>(Assumptions!D$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!D$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>(Assumptions!E$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!E$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>(Assumptions!F$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!F$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$95,Assumptions!$C$96,Assumptions!$C$97))</f>
+        <f>(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v/>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -12054,23 +12086,23 @@
         <v>0.4346</v>
       </c>
       <c r="E25" s="16">
-        <f>(Assumptions!C$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!C$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>(Assumptions!D$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!D$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>(Assumptions!E$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!E$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>(Assumptions!F$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!F$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>(Assumptions!G$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$95,Assumptions!$D$96,Assumptions!$D$97))</f>
+        <f>(Assumptions!G$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v/>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -12532,7 +12564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13268,7 +13300,11 @@
         <f>I17-I18</f>
         <v/>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>合并口径(含少数股东损益)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -13276,171 +13312,212 @@
           <t>归母净利润</t>
         </is>
       </c>
-      <c r="B20" s="35">
-        <f>B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="35">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="35">
-        <f>D19</f>
-        <v/>
+      <c r="B20" s="36" t="n">
+        <v>671.3</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>1154.4</v>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>4312</v>
       </c>
       <c r="E20" s="35">
-        <f>E19</f>
+        <f>E19*(1-Assumptions!C$42)</f>
         <v/>
       </c>
       <c r="F20" s="35">
-        <f>F19</f>
+        <f>F19*(1-Assumptions!D$42)</f>
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>G19</f>
+        <f>G19*(1-Assumptions!E$42)</f>
         <v/>
       </c>
       <c r="H20" s="35">
-        <f>H19</f>
+        <f>H19*(1-Assumptions!F$42)</f>
         <v/>
       </c>
       <c r="I20" s="35">
-        <f>I19</f>
+        <f>I19*(1-Assumptions!G$42)</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>历史: 2023A 6.7亿/2024A 11.5亿/2025A 43.1亿</t>
+          <t>历史: 2023A 6.7亿/2024A 11.5亿/2025A 43.1亿 (config硬数, 归母口径=hist.cf.np); 预测=净利润×(1-少数股东损益占比)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  归母净利率</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>B20/B4</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>C20/C4</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>D20/D4</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>E20/E4</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>F20/F4</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>G20/G4</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f>H20/H4</f>
-        <v/>
-      </c>
-      <c r="I21" s="16">
-        <f>I20/I4</f>
+          <t>少数股东损益</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>B19-B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>C19-C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>D19-D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>E19-E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>G19-G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="26">
+        <f>H19-H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="26">
+        <f>I19-I20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2025A 22.4%</t>
+          <t>＝净利润-归母净利润; 历史为合并与归母口径差(倒挤), 预测=净利润×mi_share</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  归母净利率</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B20/B4</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>C20/C4</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>D20/D4</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>E20/E4</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>F20/F4</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G20/G4</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H20/H4</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I20/I4</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>2025A 22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>EPS(元/股)</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B23" s="14">
         <f>B20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C23" s="14">
         <f>C20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D23" s="14">
         <f>D20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E23" s="14">
         <f>E20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F23" s="14">
         <f>F20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G23" s="14">
         <f>G20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="H22" s="14">
+      <c r="H23" s="14">
         <f>H20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="I22" s="14">
+      <c r="I23" s="14">
         <f>I20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>＝归母/稀释股数(Equity_Roll页, 现=9.83亿股)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>EBIT (利润总额+财务费用)</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B24" s="35">
         <f>B17+B13</f>
         <v/>
       </c>
-      <c r="C23" s="35">
+      <c r="C24" s="35">
         <f>C17+C13</f>
         <v/>
       </c>
-      <c r="D23" s="35">
+      <c r="D24" s="35">
         <f>D17+D13</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E24" s="35">
         <f>E17+E13</f>
         <v/>
       </c>
-      <c r="F23" s="35">
+      <c r="F24" s="35">
         <f>F17+F13</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G24" s="35">
         <f>G17+G13</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H24" s="35">
         <f>H17+H13</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I24" s="35">
         <f>I17+I13</f>
         <v/>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供DCF页FCFF计算</t>
         </is>
@@ -13640,23 +13717,23 @@
         <v>6061</v>
       </c>
       <c r="E6" s="26">
-        <f>Assumptions!C$45/365*IS!E4</f>
+        <f>Assumptions!C$46/365*IS!E4</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>Assumptions!D$45/365*IS!F4</f>
+        <f>Assumptions!D$46/365*IS!F4</f>
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>Assumptions!E$45/365*IS!G4</f>
+        <f>Assumptions!E$46/365*IS!G4</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>Assumptions!F$45/365*IS!H4</f>
+        <f>Assumptions!F$46/365*IS!H4</f>
         <v/>
       </c>
       <c r="I6" s="26">
-        <f>Assumptions!G$45/365*IS!I4</f>
+        <f>Assumptions!G$46/365*IS!I4</f>
         <v/>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -13681,23 +13758,23 @@
         <v>78.3</v>
       </c>
       <c r="E7" s="26">
-        <f>IS!E4*Assumptions!C$48</f>
+        <f>IS!E4*Assumptions!C$49</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>IS!F4*Assumptions!D$48</f>
+        <f>IS!F4*Assumptions!D$49</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>IS!G4*Assumptions!E$48</f>
+        <f>IS!G4*Assumptions!E$49</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>IS!H4*Assumptions!F$48</f>
+        <f>IS!H4*Assumptions!F$49</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>IS!I4*Assumptions!G$48</f>
+        <f>IS!I4*Assumptions!G$49</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -13763,23 +13840,23 @@
         <v>3162.4</v>
       </c>
       <c r="E9" s="26">
-        <f>Assumptions!C$46/365*IS!E6</f>
+        <f>Assumptions!C$47/365*IS!E6</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>Assumptions!D$46/365*IS!F6</f>
+        <f>Assumptions!D$47/365*IS!F6</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>Assumptions!E$46/365*IS!G6</f>
+        <f>Assumptions!E$47/365*IS!G6</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>Assumptions!F$46/365*IS!H6</f>
+        <f>Assumptions!F$47/365*IS!H6</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>Assumptions!G$46/365*IS!I6</f>
+        <f>Assumptions!G$47/365*IS!I6</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -14338,23 +14415,23 @@
         <v>10525.9</v>
       </c>
       <c r="E23" s="26">
-        <f>Assumptions!C$47/365*IS!E6</f>
+        <f>Assumptions!C$48/365*IS!E6</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>Assumptions!D$47/365*IS!F6</f>
+        <f>Assumptions!D$48/365*IS!F6</f>
         <v/>
       </c>
       <c r="G23" s="26">
-        <f>Assumptions!E$47/365*IS!G6</f>
+        <f>Assumptions!E$48/365*IS!G6</f>
         <v/>
       </c>
       <c r="H23" s="26">
-        <f>Assumptions!F$47/365*IS!H6</f>
+        <f>Assumptions!F$48/365*IS!H6</f>
         <v/>
       </c>
       <c r="I23" s="26">
-        <f>Assumptions!G$47/365*IS!I6</f>
+        <f>Assumptions!G$48/365*IS!I6</f>
         <v/>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -14420,23 +14497,23 @@
         <v>278.9</v>
       </c>
       <c r="E25" s="26">
-        <f>IS!E4*Assumptions!C$49</f>
+        <f>IS!E4*Assumptions!C$50</f>
         <v/>
       </c>
       <c r="F25" s="26">
-        <f>IS!F4*Assumptions!D$49</f>
+        <f>IS!F4*Assumptions!D$50</f>
         <v/>
       </c>
       <c r="G25" s="26">
-        <f>IS!G4*Assumptions!E$49</f>
+        <f>IS!G4*Assumptions!E$50</f>
         <v/>
       </c>
       <c r="H25" s="26">
-        <f>IS!H4*Assumptions!F$49</f>
+        <f>IS!H4*Assumptions!F$50</f>
         <v/>
       </c>
       <c r="I25" s="26">
-        <f>IS!I4*Assumptions!G$49</f>
+        <f>IS!I4*Assumptions!G$50</f>
         <v/>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -14461,23 +14538,23 @@
         <v>471.6</v>
       </c>
       <c r="E26" s="26">
-        <f>IS!E4*Assumptions!C$50</f>
+        <f>IS!E4*Assumptions!C$51</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!F4*Assumptions!D$50</f>
+        <f>IS!F4*Assumptions!D$51</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!G4*Assumptions!E$50</f>
+        <f>IS!G4*Assumptions!E$51</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!H4*Assumptions!F$50</f>
+        <f>IS!H4*Assumptions!F$51</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!I4*Assumptions!G$50</f>
+        <f>IS!I4*Assumptions!G$51</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -15302,35 +15379,35 @@
           <t>配平差额检查(资产-负债权益)</t>
         </is>
       </c>
-      <c r="B47" s="36">
+      <c r="B47" s="37">
         <f>B21-B46</f>
         <v/>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="37">
         <f>C21-C46</f>
         <v/>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="37">
         <f>D21-D46</f>
         <v/>
       </c>
-      <c r="E47" s="36">
+      <c r="E47" s="37">
         <f>E21-E46</f>
         <v/>
       </c>
-      <c r="F47" s="36">
+      <c r="F47" s="37">
         <f>F21-F46</f>
         <v/>
       </c>
-      <c r="G47" s="36">
+      <c r="G47" s="37">
         <f>G21-G46</f>
         <v/>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="37">
         <f>H21-H46</f>
         <v/>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="37">
         <f>I21-I46</f>
         <v/>
       </c>
@@ -15618,13 +15695,13 @@
           <t>经营活动现金流量净额</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1279.8</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="36" t="n">
         <v>1358.3</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="36" t="n">
         <v>4602.7</v>
       </c>
       <c r="E8" s="35">
@@ -15794,13 +15871,13 @@
           <t>投资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>-1999.7</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="36" t="n">
         <v>-1040.8</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="36" t="n">
         <v>-6735</v>
       </c>
       <c r="E12" s="35">
@@ -15976,13 +16053,13 @@
           <t>筹资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>733.8</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="36" t="n">
         <v>-210</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="36" t="n">
         <v>4377.5</v>
       </c>
       <c r="E16" s="35">
@@ -16107,13 +16184,13 @@
           <t>期末货币资金(=BS货币资金)</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>2141.3</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="36" t="n">
         <v>1662</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="36" t="n">
         <v>3279.6</v>
       </c>
       <c r="E19" s="35">
@@ -16843,23 +16920,23 @@
         </is>
       </c>
       <c r="E22" s="26">
-        <f>E21*Assumptions!$C$58</f>
+        <f>E21*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="F22" s="26">
-        <f>F21*Assumptions!$C$58</f>
+        <f>F21*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="G22" s="26">
-        <f>G21*Assumptions!$C$58</f>
+        <f>G21*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="H22" s="26">
-        <f>H21*Assumptions!$C$58</f>
+        <f>H21*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="I22" s="26">
-        <f>I21*Assumptions!$C$58</f>
+        <f>I21*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -16914,23 +16991,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>IS!D20*Assumptions!C$61</f>
+        <f>IS!D20*Assumptions!C$62</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!E20*Assumptions!D$61</f>
+        <f>IS!E20*Assumptions!D$62</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!F20*Assumptions!E$61</f>
+        <f>IS!F20*Assumptions!E$62</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!G20*Assumptions!F$61</f>
+        <f>IS!G20*Assumptions!F$62</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!H20*Assumptions!G$61</f>
+        <f>IS!H20*Assumptions!G$62</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -17083,23 +17160,23 @@
         </is>
       </c>
       <c r="E7" s="26">
-        <f>(E13+E14)*Assumptions!$C$54</f>
+        <f>(E13+E14)*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>(F13+F14)*Assumptions!$C$54</f>
+        <f>(F13+F14)*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>(G13+G14)*Assumptions!$C$54</f>
+        <f>(G13+G14)*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>(H13+H14)*Assumptions!$C$54</f>
+        <f>(H13+H14)*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>(I13+I14)*Assumptions!$C$54</f>
+        <f>(I13+I14)*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -17115,23 +17192,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>E6*Assumptions!$C$55+E7*Assumptions!$C$56</f>
+        <f>E6*Assumptions!$C$56+E7*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>F6*Assumptions!$C$55+F7*Assumptions!$C$56</f>
+        <f>F6*Assumptions!$C$56+F7*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>G6*Assumptions!$C$55+G7*Assumptions!$C$56</f>
+        <f>G6*Assumptions!$C$56+G7*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>H6*Assumptions!$C$55+H7*Assumptions!$C$56</f>
+        <f>H6*Assumptions!$C$56+H7*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>I6*Assumptions!$C$55+I7*Assumptions!$C$56</f>
+        <f>I6*Assumptions!$C$56+I7*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -17147,23 +17224,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>E6*Assumptions!$C$57</f>
+        <f>E6*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>F6*Assumptions!$C$57</f>
+        <f>F6*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>G6*Assumptions!$C$57</f>
+        <f>G6*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>H6*Assumptions!$C$57</f>
+        <f>H6*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>I6*Assumptions!$C$57</f>
+        <f>I6*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -17249,23 +17326,23 @@
         </is>
       </c>
       <c r="E14" s="26">
-        <f>IS!E4*Assumptions!C$53</f>
+        <f>IS!E4*Assumptions!C$54</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>IS!F4*Assumptions!D$53</f>
+        <f>IS!F4*Assumptions!D$54</f>
         <v/>
       </c>
       <c r="G14" s="26">
-        <f>IS!G4*Assumptions!E$53</f>
+        <f>IS!G4*Assumptions!E$54</f>
         <v/>
       </c>
       <c r="H14" s="26">
-        <f>IS!H4*Assumptions!F$53</f>
+        <f>IS!H4*Assumptions!F$54</f>
         <v/>
       </c>
       <c r="I14" s="26">
-        <f>IS!I4*Assumptions!G$53</f>
+        <f>IS!I4*Assumptions!G$54</f>
         <v/>
       </c>
       <c r="J14" s="11" t="inlineStr">

--- a/examples/300476_胜宏科技_估值模型.xlsx
+++ b/examples/300476_胜宏科技_估值模型.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="883">
   <si>
     <r>
       <rPr>
@@ -5862,16 +5862,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PE 35x ~ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可比中位</t>
+      <t xml:space="preserve">PE 35x </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单点（无正式可比）</t>
     </r>
   </si>
   <si>
@@ -5939,7 +5939,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">带</t>
+      <t xml:space="preserve">单点</t>
     </r>
   </si>
   <si>
@@ -6040,7 +6040,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">带</t>
+      <t xml:space="preserve">单点</t>
     </r>
     <r>
       <rPr>
@@ -39183,17 +39183,55 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY1/NTM</t>
+      <t xml:space="preserve">排除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未验证远期盈利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -39248,17 +39286,55 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY1/NTM</t>
+      <t xml:space="preserve">排除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未验证远期盈利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅参照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -39857,59 +39933,198 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">股</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">βu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中位数→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumptions WACC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">relever; βl/D/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为分析师输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">计价</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">家</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/β4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">家</t>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考行情终端</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">β</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与各公司最新年报杠杆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">可按终端数据更新</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">胜宏科技</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现价</t>
     </r>
     <r>
       <rPr>
@@ -39924,67 +40139,102 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">βu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位数→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumptions WACC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">relever; βl/D/E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为分析师输入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
+    <t xml:space="preserve">300476.SZ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026E/2027E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">归母</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一致预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现价对应</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026E PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">显著低于可比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">胜宏科技定价 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
@@ -39993,68 +40243,189 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">参考行情终端</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">β</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与各公司最新年报杠杆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可按终端数据更新</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">胜宏科技</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基于模型基准</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">归母</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">较可比中位数折让</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反映高基数与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CCL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成本风险</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
@@ -40063,211 +40434,12 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现价</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">300476.SZ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E/2027E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">归母</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一致预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现价对应</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">显著低于可比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">胜宏科技定价 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基于模型基准</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">归母</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F3864"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下限</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">较可比中位数折让</t>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无可比公司配置</t>
     </r>
     <r>
       <rPr>
@@ -40286,143 +40458,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">反映高基数与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CCL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">成本风险</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上限</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝计价可比</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026E PE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">含海外</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; ref_only</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标记的仅参照行不参与</t>
+      <t xml:space="preserve">兜底</t>
     </r>
     <r>
       <rPr>
@@ -46864,7 +46900,7 @@
     <numFmt numFmtId="174" formatCode="0.0\x"/>
     <numFmt numFmtId="175" formatCode="0\x"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -47086,6 +47122,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF0033CC"/>
       <name val="Microsoft YaHei"/>
       <family val="0"/>
@@ -47180,7 +47223,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -47281,10 +47324,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -47294,6 +47333,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -47421,11 +47464,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -47437,15 +47484,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -47469,11 +47516,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -47923,7 +47970,7 @@
       </c>
       <c r="C23" s="4" t="str">
         <f aca="false">TEXT(Relative_Val!C17,"0.00")&amp;" ~ "&amp;TEXT(Relative_Val!C18,"0.00")</f>
-        <v>296.47 ~ 417.23</v>
+        <v>296.47 ~ 296.47</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48258,18 +48305,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>500</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -48295,7 +48342,7 @@
         <f aca="false">H63</f>
         <v>1627.5040887566</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>501</v>
       </c>
     </row>
@@ -48323,7 +48370,7 @@
         <f aca="false">CF!I8</f>
         <v>26172.617975231</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>503</v>
       </c>
     </row>
@@ -48351,7 +48398,7 @@
         <f aca="false">-PPE!I14+PPE!I9</f>
         <v>-7837.76163733495</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>505</v>
       </c>
     </row>
@@ -48379,7 +48426,7 @@
         <f aca="false">-Schedules!I26</f>
         <v>-6013.04709324918</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>507</v>
       </c>
     </row>
@@ -48407,7 +48454,7 @@
         <f aca="false">-I64</f>
         <v>-0.0517499999999999</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>509</v>
       </c>
     </row>
@@ -48435,7 +48482,7 @@
         <f aca="false">-(I20+I31+I39+I49)</f>
         <v>-2.3</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>511</v>
       </c>
     </row>
@@ -48463,7 +48510,7 @@
         <f aca="false">I6+I7+I8+I9+I10+I11</f>
         <v>13946.9615834035</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>513</v>
       </c>
     </row>
@@ -48491,7 +48538,7 @@
         <f aca="false">IS!I4*Assumptions!$C$66</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>515</v>
       </c>
     </row>
@@ -48519,7 +48566,7 @@
         <f aca="false">MAX(0,I13-I12)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>517</v>
       </c>
     </row>
@@ -48547,7 +48594,7 @@
         <f aca="false">MAX(0,I12+I14-I13)</f>
         <v>12126.4572960851</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>519</v>
       </c>
     </row>
@@ -48589,7 +48636,7 @@
         <f aca="false">H24</f>
         <v>0</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -48617,7 +48664,7 @@
         <f aca="false">Assumptions!G$67</f>
         <v>0</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>524</v>
       </c>
     </row>
@@ -48645,7 +48692,7 @@
         <f aca="false">MIN(I19,I18)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>526</v>
       </c>
     </row>
@@ -48673,7 +48720,7 @@
         <f aca="false">I14</f>
         <v>0</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>528</v>
       </c>
     </row>
@@ -48701,7 +48748,7 @@
         <f aca="false">I18-I20+I21</f>
         <v>0</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>530</v>
       </c>
     </row>
@@ -48729,7 +48776,7 @@
         <f aca="false">MIN(I15,I22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>532</v>
       </c>
     </row>
@@ -48761,7 +48808,7 @@
         <f aca="false">I22-I23</f>
         <v>0</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>534</v>
       </c>
     </row>
@@ -48789,7 +48836,7 @@
         <f aca="false">(I18+I24)/2</f>
         <v>0</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>536</v>
       </c>
     </row>
@@ -48817,7 +48864,7 @@
         <f aca="false">I25*Assumptions!$C$71</f>
         <v>0</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>538</v>
       </c>
     </row>
@@ -48859,7 +48906,7 @@
         <f aca="false">H32</f>
         <v>0</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -48887,7 +48934,7 @@
         <f aca="false">Assumptions!G$68</f>
         <v>300</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="J30" s="28" t="s">
         <v>540</v>
       </c>
     </row>
@@ -48915,7 +48962,7 @@
         <f aca="false">MIN(I30,I29)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J31" s="28" t="s">
         <v>526</v>
       </c>
     </row>
@@ -48947,7 +48994,7 @@
         <f aca="false">I29-I31</f>
         <v>0</v>
       </c>
-      <c r="J32" s="25" t="s">
+      <c r="J32" s="28" t="s">
         <v>541</v>
       </c>
     </row>
@@ -48975,7 +49022,7 @@
         <f aca="false">(I29+I32)/2</f>
         <v>0</v>
       </c>
-      <c r="J33" s="25" t="s">
+      <c r="J33" s="28" t="s">
         <v>536</v>
       </c>
     </row>
@@ -49003,7 +49050,7 @@
         <f aca="false">I33*Assumptions!$C$72</f>
         <v>0</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="28" t="s">
         <v>538</v>
       </c>
     </row>
@@ -49045,7 +49092,7 @@
         <f aca="false">H42</f>
         <v>0</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -49073,7 +49120,7 @@
         <f aca="false">Assumptions!G$69</f>
         <v>500</v>
       </c>
-      <c r="J38" s="25" t="s">
+      <c r="J38" s="28" t="s">
         <v>543</v>
       </c>
     </row>
@@ -49101,7 +49148,7 @@
         <f aca="false">MIN(I38,I37)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="25" t="s">
+      <c r="J39" s="28" t="s">
         <v>526</v>
       </c>
     </row>
@@ -49129,7 +49176,7 @@
         <f aca="false">I37-I39</f>
         <v>0</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="J40" s="28" t="s">
         <v>530</v>
       </c>
     </row>
@@ -49157,7 +49204,7 @@
         <f aca="false">MIN(I15-I23,I40)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="25" t="s">
+      <c r="J41" s="28" t="s">
         <v>532</v>
       </c>
     </row>
@@ -49189,7 +49236,7 @@
         <f aca="false">I40-I41</f>
         <v>0</v>
       </c>
-      <c r="J42" s="25" t="s">
+      <c r="J42" s="28" t="s">
         <v>534</v>
       </c>
     </row>
@@ -49217,7 +49264,7 @@
         <f aca="false">(I37+I42)/2</f>
         <v>0</v>
       </c>
-      <c r="J43" s="25" t="s">
+      <c r="J43" s="28" t="s">
         <v>536</v>
       </c>
     </row>
@@ -49245,7 +49292,7 @@
         <f aca="false">I43*Assumptions!$C$73</f>
         <v>0</v>
       </c>
-      <c r="J44" s="25" t="s">
+      <c r="J44" s="28" t="s">
         <v>538</v>
       </c>
     </row>
@@ -49287,7 +49334,7 @@
         <f aca="false">H50</f>
         <v>2.3</v>
       </c>
-      <c r="J47" s="25" t="s">
+      <c r="J47" s="28" t="s">
         <v>522</v>
       </c>
     </row>
@@ -49315,7 +49362,7 @@
         <f aca="false">Assumptions!G$70</f>
         <v>20</v>
       </c>
-      <c r="J48" s="25" t="s">
+      <c r="J48" s="28" t="s">
         <v>545</v>
       </c>
     </row>
@@ -49343,7 +49390,7 @@
         <f aca="false">MIN(I48,I47)</f>
         <v>2.3</v>
       </c>
-      <c r="J49" s="25" t="s">
+      <c r="J49" s="28" t="s">
         <v>526</v>
       </c>
     </row>
@@ -49375,7 +49422,7 @@
         <f aca="false">I47-I49</f>
         <v>0</v>
       </c>
-      <c r="J50" s="25" t="s">
+      <c r="J50" s="28" t="s">
         <v>541</v>
       </c>
     </row>
@@ -49403,7 +49450,7 @@
         <f aca="false">(I47+I50)/2</f>
         <v>1.15</v>
       </c>
-      <c r="J51" s="25" t="s">
+      <c r="J51" s="28" t="s">
         <v>536</v>
       </c>
     </row>
@@ -49431,23 +49478,23 @@
         <f aca="false">I51*Assumptions!$C$74</f>
         <v>0.0517499999999999</v>
       </c>
-      <c r="J52" s="25" t="s">
+      <c r="J52" s="28" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>546</v>
       </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
@@ -49477,7 +49524,7 @@
         <f aca="false">I18+I29+I37+I47</f>
         <v>2.3</v>
       </c>
-      <c r="J55" s="25" t="s">
+      <c r="J55" s="28" t="s">
         <v>548</v>
       </c>
     </row>
@@ -49509,7 +49556,7 @@
         <f aca="false">I24+I32+I42+I50</f>
         <v>0</v>
       </c>
-      <c r="J56" s="25" t="s">
+      <c r="J56" s="28" t="s">
         <v>550</v>
       </c>
     </row>
@@ -49537,7 +49584,7 @@
         <f aca="false">I56-I55</f>
         <v>-2.3</v>
       </c>
-      <c r="J57" s="25" t="s">
+      <c r="J57" s="28" t="s">
         <v>552</v>
       </c>
     </row>
@@ -49565,7 +49612,7 @@
         <f aca="false">I23+I41</f>
         <v>0</v>
       </c>
-      <c r="J58" s="25" t="s">
+      <c r="J58" s="28" t="s">
         <v>554</v>
       </c>
     </row>
@@ -49593,7 +49640,7 @@
         <f aca="false">I15-I58</f>
         <v>12126.4572960851</v>
       </c>
-      <c r="J59" s="25" t="s">
+      <c r="J59" s="28" t="s">
         <v>556</v>
       </c>
     </row>
@@ -49621,7 +49668,7 @@
         <f aca="false">H61</f>
         <v>18508.514141763</v>
       </c>
-      <c r="J60" s="27" t="s">
+      <c r="J60" s="26" t="s">
         <v>558</v>
       </c>
     </row>
@@ -49653,7 +49700,7 @@
         <f aca="false">I60+I59</f>
         <v>30634.9714378481</v>
       </c>
-      <c r="J61" s="25" t="s">
+      <c r="J61" s="28" t="s">
         <v>560</v>
       </c>
     </row>
@@ -49681,7 +49728,7 @@
         <f aca="false">I61-I60</f>
         <v>12126.4572960851</v>
       </c>
-      <c r="J62" s="25" t="s">
+      <c r="J62" s="28" t="s">
         <v>562</v>
       </c>
     </row>
@@ -49713,7 +49760,7 @@
         <f aca="false">I12+I14-I58-I59</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J63" s="25" t="s">
+      <c r="J63" s="28" t="s">
         <v>564</v>
       </c>
     </row>
@@ -49741,7 +49788,7 @@
         <f aca="false">I130</f>
         <v>0.0517499999999999</v>
       </c>
-      <c r="J64" s="25" t="s">
+      <c r="J64" s="28" t="s">
         <v>566</v>
       </c>
     </row>
@@ -49769,7 +49816,7 @@
         <f aca="false">I132</f>
         <v>20.68805025645</v>
       </c>
-      <c r="J65" s="25" t="s">
+      <c r="J65" s="28" t="s">
         <v>568</v>
       </c>
     </row>
@@ -49797,7 +49844,7 @@
         <f aca="false">Assumptions!$C$76</f>
         <v>30</v>
       </c>
-      <c r="J66" s="25" t="s">
+      <c r="J66" s="28" t="s">
         <v>570</v>
       </c>
     </row>
@@ -49825,23 +49872,23 @@
         <f aca="false">I133</f>
         <v>9.36369974355002</v>
       </c>
-      <c r="J67" s="25" t="s">
+      <c r="J67" s="28" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="25" t="s">
         <v>573</v>
       </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
@@ -51414,18 +51461,18 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="26" t="s">
+      <c r="A136" s="25" t="s">
         <v>639</v>
       </c>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="26"/>
-      <c r="E136" s="26"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="26"/>
-      <c r="H136" s="26"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="26"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="25"/>
+      <c r="H136" s="25"/>
+      <c r="I136" s="25"/>
+      <c r="J136" s="25"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
@@ -51451,7 +51498,7 @@
         <f aca="false">ABS(I64-(I26+I34+I44+I52))</f>
         <v>0</v>
       </c>
-      <c r="J137" s="25" t="s">
+      <c r="J137" s="28" t="s">
         <v>641</v>
       </c>
     </row>
@@ -51479,7 +51526,7 @@
         <f aca="false">ABS(I65-(I6+I63)/2*Assumptions!$C$75)</f>
         <v>0</v>
       </c>
-      <c r="J138" s="25" t="s">
+      <c r="J138" s="28" t="s">
         <v>643</v>
       </c>
     </row>
@@ -51507,7 +51554,7 @@
         <f aca="false">MAX(I137,I138)</f>
         <v>0</v>
       </c>
-      <c r="J139" s="25" t="s">
+      <c r="J139" s="28" t="s">
         <v>645</v>
       </c>
     </row>
@@ -51535,7 +51582,7 @@
         <f aca="false">I139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J140" s="25"/>
+      <c r="J140" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -51671,7 +51718,7 @@
         <f aca="false">H5</f>
         <v>870.3</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>649</v>
       </c>
     </row>
@@ -51708,7 +51755,7 @@
         <f aca="false">H6</f>
         <v>5387.3</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -51745,7 +51792,7 @@
         <f aca="false">H7</f>
         <v>5.4</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -51782,7 +51829,7 @@
         <f aca="false">H8</f>
         <v>1994.3</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>651</v>
       </c>
     </row>
@@ -51810,7 +51857,7 @@
         <f aca="false">IS!I20*Assumptions!$C$63</f>
         <v>2176.46655616801</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>653</v>
       </c>
     </row>
@@ -51847,7 +51894,7 @@
         <f aca="false">H10+I9</f>
         <v>8538.68509474164</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>655</v>
       </c>
     </row>
@@ -51875,7 +51922,7 @@
         <f aca="false">Schedules!I26</f>
         <v>6013.04709324918</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>657</v>
       </c>
     </row>
@@ -51912,7 +51959,7 @@
         <f aca="false">H12+IS!I20-I11-I9</f>
         <v>61493.1102369538</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>659</v>
       </c>
     </row>
@@ -51949,7 +51996,7 @@
         <f aca="false">H13</f>
         <v>9.1</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>661</v>
       </c>
     </row>
@@ -51989,7 +52036,7 @@
         <f aca="false">I5+I6-I7+I8+I10+I12+I13</f>
         <v>78287.3953316955</v>
       </c>
-      <c r="J14" s="25"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
@@ -52024,7 +52071,7 @@
         <f aca="false">H15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -52062,21 +52109,21 @@
         <f aca="false">I14+I15</f>
         <v>78287.3953316955</v>
       </c>
-      <c r="J16" s="25"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
@@ -52086,7 +52133,7 @@
         <f aca="false">Assumptions!$C$8</f>
         <v>983</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>664</v>
       </c>
     </row>
@@ -52097,7 +52144,7 @@
       <c r="C20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>666</v>
       </c>
     </row>
@@ -52109,7 +52156,7 @@
         <f aca="false">C19+C20</f>
         <v>983</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>668</v>
       </c>
     </row>
@@ -52217,7 +52264,7 @@
         <f aca="false">IS!I24</f>
         <v>25465.112894691</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>672</v>
       </c>
     </row>
@@ -52245,7 +52292,7 @@
         <f aca="false">Assumptions!G$41</f>
         <v>0.145</v>
       </c>
-      <c r="J5" s="25"/>
+      <c r="J5" s="28"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -52271,7 +52318,7 @@
         <f aca="false">I4*(1-I5)</f>
         <v>21772.6715249608</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
@@ -52297,7 +52344,7 @@
         <f aca="false">PPE!I19</f>
         <v>4646.05484871961</v>
       </c>
-      <c r="J7" s="25"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
@@ -52323,7 +52370,7 @@
         <f aca="false">Schedules!I18</f>
         <v>238.154185168642</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="26" t="s">
         <v>677</v>
       </c>
     </row>
@@ -52351,7 +52398,7 @@
         <f aca="false">PPE!I14</f>
         <v>8192.26929293281</v>
       </c>
-      <c r="J9" s="25"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
@@ -52377,7 +52424,7 @@
         <f aca="false">I6+I7-I8-I9</f>
         <v>17988.302895579</v>
       </c>
-      <c r="J10" s="25"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
@@ -52398,7 +52445,7 @@
       <c r="I11" s="55" t="n">
         <v>4.5</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>681</v>
       </c>
     </row>
@@ -52426,7 +52473,7 @@
         <f aca="false">1/(1+Assumptions!$C$91)^I11</f>
         <v>0.720337339547877</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -52452,7 +52499,7 @@
         <f aca="false">I10*I12</f>
         <v>12957.6462507827</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -52462,7 +52509,7 @@
         <f aca="false">SUM(E13:I13)</f>
         <v>42244.5313644785</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -52472,7 +52519,7 @@
         <f aca="false">I10*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)</f>
         <v>406140.709665457</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>686</v>
       </c>
     </row>
@@ -52484,7 +52531,7 @@
         <f aca="false">D16*I12</f>
         <v>292558.318282502</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>688</v>
       </c>
     </row>
@@ -52496,7 +52543,7 @@
         <f aca="false">D15+D17</f>
         <v>334802.84964698</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
@@ -52506,7 +52553,7 @@
         <f aca="false">BS!D4</f>
         <v>3279.6</v>
       </c>
-      <c r="J19" s="25"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
@@ -52516,7 +52563,7 @@
         <f aca="false">BS!D5</f>
         <v>137</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
@@ -52526,7 +52573,7 @@
         <f aca="false">BS!D18</f>
         <v>2854.3</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>693</v>
       </c>
     </row>
@@ -52538,7 +52585,7 @@
         <f aca="false">-(BS!D22+BS!D28+BS!D31+BS!D32)</f>
         <v>-6445.6</v>
       </c>
-      <c r="J22" s="25"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -52548,7 +52595,7 @@
         <f aca="false">-BS!D44</f>
         <v>-0</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="26" t="s">
         <v>696</v>
       </c>
     </row>
@@ -52560,7 +52607,7 @@
         <f aca="false">D19+D20+D21+D22+D23</f>
         <v>-174.700000000001</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>698</v>
       </c>
     </row>
@@ -52572,7 +52619,7 @@
         <f aca="false">D18+D24</f>
         <v>334628.14964698</v>
       </c>
-      <c r="J25" s="25"/>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
@@ -52582,7 +52629,7 @@
         <f aca="false">D25/Equity_Roll!$C$21</f>
         <v>340.415208186145</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>701</v>
       </c>
     </row>
@@ -52594,7 +52641,7 @@
         <f aca="false">Assumptions!$C$7</f>
         <v>269.33</v>
       </c>
-      <c r="J27" s="25"/>
+      <c r="J27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
@@ -52604,7 +52651,7 @@
         <f aca="false">D26/D27-1</f>
         <v>0.263933494917553</v>
       </c>
-      <c r="J28" s="25"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
@@ -52614,7 +52661,7 @@
         <f aca="false">D25/IS!E20</f>
         <v>40.1884888104101</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>705</v>
       </c>
     </row>
@@ -52626,7 +52673,7 @@
         <f aca="false">D18/(IS!E24+PPE!E19)</f>
         <v>29.1339285066862</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
@@ -52746,7 +52793,7 @@
         <f aca="false">IS!I20</f>
         <v>21764.6655616801</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>710</v>
       </c>
     </row>
@@ -52774,7 +52821,7 @@
         <f aca="false">PPE!I19</f>
         <v>4646.05484871961</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>711</v>
       </c>
     </row>
@@ -52802,7 +52849,7 @@
         <f aca="false">Schedules!I18</f>
         <v>238.154185168642</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>712</v>
       </c>
     </row>
@@ -52830,7 +52877,7 @@
         <f aca="false">PPE!I14</f>
         <v>8192.26929293281</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>713</v>
       </c>
     </row>
@@ -52858,7 +52905,7 @@
         <f aca="false">FIN!I57</f>
         <v>-2.3</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>715</v>
       </c>
     </row>
@@ -52886,7 +52933,7 @@
         <f aca="false">-FIN!I62</f>
         <v>-12126.4572960851</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>717</v>
       </c>
     </row>
@@ -52914,7 +52961,7 @@
         <f aca="false">I4+I5-I6-I7+I8</f>
         <v>17977.9969322982</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>719</v>
       </c>
     </row>
@@ -52937,7 +52984,7 @@
       <c r="I11" s="55" t="n">
         <v>4.5</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>720</v>
       </c>
     </row>
@@ -52965,7 +53012,7 @@
         <f aca="false">1/(1+KE)^I11</f>
         <v>0.716931901751695</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>722</v>
       </c>
     </row>
@@ -52993,7 +53040,7 @@
         <f aca="false">I10*I12</f>
         <v>12888.9995303587</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -53003,7 +53050,7 @@
         <f aca="false">SUM(E13:I13)</f>
         <v>35927.4268663414</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -53013,7 +53060,7 @@
         <f aca="false">I10-I8+FIN!I56*TERM_G</f>
         <v>17980.2969322982</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>725</v>
       </c>
     </row>
@@ -53025,7 +53072,7 @@
         <f aca="false">D16*(1+TERM_G)/(KE-TERM_G)</f>
         <v>396119.481704931</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>727</v>
       </c>
     </row>
@@ -53037,7 +53084,7 @@
         <f aca="false">D17*I12</f>
         <v>283990.693339612</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>728</v>
       </c>
     </row>
@@ -53049,7 +53096,7 @@
         <f aca="false">D15+D18</f>
         <v>319918.120205954</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="26" t="s">
         <v>730</v>
       </c>
     </row>
@@ -53061,7 +53108,7 @@
         <f aca="false">D19/SHARES_DIL</f>
         <v>325.450783525894</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>731</v>
       </c>
     </row>
@@ -53073,7 +53120,7 @@
         <f aca="false">DCF!D26</f>
         <v>340.415208186145</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>733</v>
       </c>
     </row>
@@ -53085,7 +53132,7 @@
         <f aca="false">D20/D21-1</f>
         <v>-0.0439593305480879</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="26" t="s">
         <v>735</v>
       </c>
     </row>
@@ -53097,7 +53144,7 @@
         <f aca="false">IF(""&lt;&gt;"","WAIVED: ",IF(ABS(D22)&gt;=0.3,"警告: 差异≥30%, 复核债务调度/资本结构/终值","通过: 差异&lt;30%"))</f>
         <v>通过: 差异&lt;30%</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>736</v>
       </c>
     </row>
@@ -53505,17 +53552,11 @@
       <c r="A10" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="F10" s="60" t="n">
-        <f aca="false">MEDIAN(F5:F6)</f>
-        <v>49.2571841680777</v>
-      </c>
-      <c r="H10" s="60" t="n">
-        <f aca="false">MEDIAN(H5:H6)</f>
-        <v>38.0318629731674</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <f aca="false">MEDIAN(J5:J6)</f>
-        <v>1.67718874868117</v>
+      <c r="H10" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="J10" s="60" t="s">
+        <v>272</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>772</v>
@@ -53543,7 +53584,7 @@
         <f aca="false">Assumptions!$C$13/100</f>
         <v>91.2</v>
       </c>
-      <c r="F11" s="60" t="n">
+      <c r="F11" s="62" t="n">
         <f aca="false">C11/E11</f>
         <v>29.0297576754386</v>
       </c>
@@ -53560,32 +53601,32 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>776</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="C14" s="62" t="n">
+      <c r="C14" s="63" t="n">
         <v>35</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="28" t="s">
         <v>778</v>
       </c>
     </row>
@@ -53594,10 +53635,10 @@
         <v>779</v>
       </c>
       <c r="C15" s="57" t="n">
-        <f aca="false">F10</f>
-        <v>49.2571841680777</v>
-      </c>
-      <c r="K15" s="25" t="s">
+        <f aca="false">C14</f>
+        <v>35</v>
+      </c>
+      <c r="K15" s="28" t="s">
         <v>780</v>
       </c>
     </row>
@@ -53625,7 +53666,7 @@
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">C15*C16/Equity_Roll!$C$21</f>
-        <v>417.231279393019</v>
+        <v>296.466292691972</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53638,9 +53679,9 @@
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">C15*Assumptions!$C$13/Equity_Roll!$C$21</f>
-        <v>456.994424835064</v>
-      </c>
-      <c r="K19" s="25" t="s">
+        <v>324.72024415056</v>
+      </c>
+      <c r="K19" s="28" t="s">
         <v>785</v>
       </c>
     </row>
@@ -53654,7 +53695,7 @@
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">C18/Assumptions!$C$7-1</f>
-        <v>0.54914520993955</v>
+        <v>0.1007548089406</v>
       </c>
     </row>
   </sheetData>
@@ -53715,17 +53756,17 @@
       <c r="J2" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>789</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
@@ -53817,7 +53858,7 @@
         <f aca="false">(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>309.715644088754</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="64" t="n">
         <f aca="false">(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>340.415208186145</v>
       </c>
@@ -53883,48 +53924,48 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="28" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
         <v>793</v>
       </c>
-      <c r="C14" s="64" t="n">
+      <c r="C14" s="65" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="64" t="n">
+      <c r="D14" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="65" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="64" t="n">
+      <c r="F14" s="65" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="64" t="n">
+      <c r="G14" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c r="H14" s="65" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="65" t="n">
+      <c r="B15" s="66" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="8" t="n">
@@ -53953,7 +53994,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="65" t="n">
+      <c r="B16" s="66" t="n">
         <v>0.6</v>
       </c>
       <c r="C16" s="8" t="n">
@@ -53982,7 +54023,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="65" t="n">
+      <c r="B17" s="66" t="n">
         <v>0.8</v>
       </c>
       <c r="C17" s="8" t="n">
@@ -54011,7 +54052,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="65" t="n">
+      <c r="B18" s="66" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="8" t="n">
@@ -54040,7 +54081,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="65" t="n">
+      <c r="B19" s="66" t="n">
         <v>1.115</v>
       </c>
       <c r="C19" s="8" t="n">
@@ -54051,7 +54092,7 @@
         <f aca="false">IS!$D$20*(1+$B19)*D$14/Equity_Roll!$C$21</f>
         <v>278.327975584944</v>
       </c>
-      <c r="E19" s="63" t="n">
+      <c r="E19" s="64" t="n">
         <f aca="false">IS!$D$20*(1+$B19)*E$14/Equity_Roll!$C$21</f>
         <v>324.715971515768</v>
       </c>
@@ -54069,7 +54110,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="65" t="n">
+      <c r="B20" s="66" t="n">
         <v>1.3</v>
       </c>
       <c r="C20" s="8" t="n">
@@ -54098,22 +54139,22 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="28" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>795</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
@@ -54130,7 +54171,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="66" t="n">
+      <c r="B25" s="67" t="n">
         <v>-40</v>
       </c>
       <c r="C25" s="8" t="n">
@@ -54143,7 +54184,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="66" t="n">
+      <c r="B26" s="67" t="n">
         <v>-20</v>
       </c>
       <c r="C26" s="8" t="n">
@@ -54156,10 +54197,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="66" t="n">
+      <c r="B27" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="63" t="n">
+      <c r="C27" s="64" t="n">
         <f aca="false">((DCF!E$10+$B27/365*(IS!E$6))/(1+Assumptions!$C$91)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$91)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$91)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$91)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$91)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>340.415208186145</v>
       </c>
@@ -54169,7 +54210,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="66" t="n">
+      <c r="B28" s="67" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="8" t="n">
@@ -54182,7 +54223,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="66" t="n">
+      <c r="B29" s="67" t="n">
         <v>40</v>
       </c>
       <c r="C29" s="8" t="n">
@@ -54195,7 +54236,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="26" t="s">
         <v>800</v>
       </c>
     </row>
@@ -54262,15 +54303,15 @@
       <c r="A3" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="B3" s="67" t="n">
+      <c r="B3" s="68" t="n">
         <f aca="false">Assumptions!$C$5</f>
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="str">
+      <c r="C3" s="69" t="str">
         <f aca="false">CHOOSE(B3,"熊市","基准","牛市")</f>
         <v>基准</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="28" t="s">
         <v>804</v>
       </c>
     </row>
@@ -54282,23 +54323,23 @@
         <f aca="false">Schedules!E17/IS!E4</f>
         <v>-0.072190951343209</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>807</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -54428,7 +54469,7 @@
         <f aca="false">(E11/(1+Assumptions!$C$91)^0.5+F11/(1+Assumptions!$C$91)^1.5+G11/(1+Assumptions!$C$91)^2.5+H11/(1+Assumptions!$C$91)^3.5+I11/(1+Assumptions!$C$91)^4.5+I11*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>131.019146018866</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>811</v>
       </c>
     </row>
@@ -54437,26 +54478,26 @@
         <v>812</v>
       </c>
       <c r="B13" s="23" t="n">
-        <f aca="false">E10*Relative_Val!$F$10/Equity_Roll!$C$21</f>
-        <v>343.749007183502</v>
-      </c>
-      <c r="J13" s="25" t="s">
+        <f aca="false">E10*Relative_Val!$C$14/Equity_Roll!$C$21</f>
+        <v>244.253005010784</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>814</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -54586,7 +54627,7 @@
         <f aca="false">(E20/(1+Assumptions!$C$91)^0.5+F20/(1+Assumptions!$C$91)^1.5+G20/(1+Assumptions!$C$91)^2.5+H20/(1+Assumptions!$C$91)^3.5+I20/(1+Assumptions!$C$91)^4.5+I20*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>350.04158085191</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>811</v>
       </c>
     </row>
@@ -54595,26 +54636,26 @@
         <v>812</v>
       </c>
       <c r="B22" s="23" t="n">
-        <f aca="false">E19*Relative_Val!$F$10/Equity_Roll!$C$21</f>
-        <v>419.232239910317</v>
-      </c>
-      <c r="J22" s="25" t="s">
+        <f aca="false">E19*Relative_Val!$C$14/Equity_Roll!$C$21</f>
+        <v>297.888087690777</v>
+      </c>
+      <c r="J22" s="28" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>815</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -54744,7 +54785,7 @@
         <f aca="false">(E29/(1+Assumptions!$C$91)^0.5+F29/(1+Assumptions!$C$91)^1.5+G29/(1+Assumptions!$C$91)^2.5+H29/(1+Assumptions!$C$91)^3.5+I29/(1+Assumptions!$C$91)^4.5+I29*(1+Assumptions!$C$92)/(Assumptions!$C$91-Assumptions!$C$92)/(1+Assumptions!$C$91)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v>569.149789174625</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="J30" s="28" t="s">
         <v>811</v>
       </c>
     </row>
@@ -54753,26 +54794,26 @@
         <v>812</v>
       </c>
       <c r="B31" s="23" t="n">
-        <f aca="false">E28*Relative_Val!$F$10/Equity_Roll!$C$21</f>
-        <v>466.174929444805</v>
-      </c>
-      <c r="J31" s="25" t="s">
+        <f aca="false">E28*Relative_Val!$C$14/Equity_Roll!$C$21</f>
+        <v>331.243509066486</v>
+      </c>
+      <c r="J31" s="28" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="25" t="s">
         <v>816</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
@@ -54782,7 +54823,7 @@
         <f aca="false">DCF!D26</f>
         <v>340.415208186145</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="28" t="s">
         <v>818</v>
       </c>
     </row>
@@ -54803,7 +54844,7 @@
         <f aca="false">B34/B21</f>
         <v>0.972499345242535</v>
       </c>
-      <c r="J36" s="25" t="s">
+      <c r="J36" s="28" t="s">
         <v>821</v>
       </c>
     </row>
@@ -54811,24 +54852,24 @@
       <c r="A37" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="B37" s="69" t="str">
+      <c r="B37" s="70" t="str">
         <f aca="false">IF(ABS(B36-1)&gt;=0.3,"警告: 桥接差异≥30%, 复核简化假设","通过: 桥接差异&lt;30%")</f>
         <v>通过: 桥接差异&lt;30%</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
@@ -54895,15 +54936,15 @@
       </c>
       <c r="B42" s="8" t="n">
         <f aca="false">B13</f>
-        <v>343.749007183502</v>
+        <v>244.253005010784</v>
       </c>
       <c r="C42" s="8" t="n">
         <f aca="false">B22</f>
-        <v>419.232239910317</v>
+        <v>297.888087690777</v>
       </c>
       <c r="D42" s="8" t="n">
         <f aca="false">B31</f>
-        <v>466.174929444805</v>
+        <v>331.243509066486</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55020,39 +55061,39 @@
       <c r="A4" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="B4" s="70" t="b">
+      <c r="B4" s="71" t="b">
         <f aca="false">ABS(BS!B47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="C4" s="70" t="b">
+      <c r="C4" s="71" t="b">
         <f aca="false">ABS(BS!C47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="D4" s="70" t="b">
+      <c r="D4" s="71" t="b">
         <f aca="false">ABS(BS!D47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="E4" s="70" t="b">
+      <c r="E4" s="71" t="b">
         <f aca="false">ABS(BS!E47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F4" s="70" t="b">
+      <c r="F4" s="71" t="b">
         <f aca="false">ABS(BS!F47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G4" s="70" t="b">
+      <c r="G4" s="71" t="b">
         <f aca="false">ABS(BS!G47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H4" s="70" t="b">
+      <c r="H4" s="71" t="b">
         <f aca="false">ABS(BS!H47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I4" s="70" t="b">
+      <c r="I4" s="71" t="b">
         <f aca="false">ABS(BS!I47)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>839</v>
       </c>
     </row>
@@ -55060,27 +55101,27 @@
       <c r="A5" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="E5" s="70" t="b">
+      <c r="E5" s="71" t="b">
         <f aca="false">ABS(CF!E19-BS!E4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F5" s="70" t="b">
+      <c r="F5" s="71" t="b">
         <f aca="false">ABS(CF!F19-BS!F4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G5" s="70" t="b">
+      <c r="G5" s="71" t="b">
         <f aca="false">ABS(CF!G19-BS!G4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H5" s="70" t="b">
+      <c r="H5" s="71" t="b">
         <f aca="false">ABS(CF!H19-BS!H4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I5" s="70" t="b">
+      <c r="I5" s="71" t="b">
         <f aca="false">ABS(CF!I19-BS!I4)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>841</v>
       </c>
     </row>
@@ -55088,27 +55129,27 @@
       <c r="A6" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="E6" s="70" t="b">
+      <c r="E6" s="71" t="b">
         <f aca="false">ABS(BS!E41-BS!D41-IS!E20+Schedules!E26+Equity_Roll!E9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F6" s="70" t="b">
+      <c r="F6" s="71" t="b">
         <f aca="false">ABS(BS!F41-BS!E41-IS!F20+Schedules!F26+Equity_Roll!F9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G6" s="70" t="b">
+      <c r="G6" s="71" t="b">
         <f aca="false">ABS(BS!G41-BS!F41-IS!G20+Schedules!G26+Equity_Roll!G9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H6" s="70" t="b">
+      <c r="H6" s="71" t="b">
         <f aca="false">ABS(BS!H41-BS!G41-IS!H20+Schedules!H26+Equity_Roll!H9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I6" s="70" t="b">
+      <c r="I6" s="71" t="b">
         <f aca="false">ABS(BS!I41-BS!H41-IS!I20+Schedules!I26+Equity_Roll!I9)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>843</v>
       </c>
     </row>
@@ -55116,39 +55157,39 @@
       <c r="A7" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="B7" s="70" t="b">
+      <c r="B7" s="71" t="b">
         <f aca="false">ABS(IS!B4-Revenue_Segments!B29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="C7" s="70" t="b">
+      <c r="C7" s="71" t="b">
         <f aca="false">ABS(IS!C4-Revenue_Segments!C29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="D7" s="70" t="b">
+      <c r="D7" s="71" t="b">
         <f aca="false">ABS(IS!D4-Revenue_Segments!D29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="E7" s="70" t="b">
+      <c r="E7" s="71" t="b">
         <f aca="false">ABS(IS!E4-Revenue_Segments!E29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F7" s="70" t="b">
+      <c r="F7" s="71" t="b">
         <f aca="false">ABS(IS!F4-Revenue_Segments!F29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G7" s="70" t="b">
+      <c r="G7" s="71" t="b">
         <f aca="false">ABS(IS!G4-Revenue_Segments!G29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H7" s="70" t="b">
+      <c r="H7" s="71" t="b">
         <f aca="false">ABS(IS!H4-Revenue_Segments!H29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I7" s="70" t="b">
+      <c r="I7" s="71" t="b">
         <f aca="false">ABS(IS!I4-Revenue_Segments!I29)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>845</v>
       </c>
     </row>
@@ -55156,39 +55197,39 @@
       <c r="A8" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="B8" s="70" t="b">
+      <c r="B8" s="71" t="b">
         <f aca="false">AND(IS!B8&gt;0,IS!B8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="70" t="b">
+      <c r="C8" s="71" t="b">
         <f aca="false">AND(IS!C8&gt;0,IS!C8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="70" t="b">
+      <c r="D8" s="71" t="b">
         <f aca="false">AND(IS!D8&gt;0,IS!D8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="70" t="b">
+      <c r="E8" s="71" t="b">
         <f aca="false">AND(IS!E8&gt;0,IS!E8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="70" t="b">
+      <c r="F8" s="71" t="b">
         <f aca="false">AND(IS!F8&gt;0,IS!F8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="70" t="b">
+      <c r="G8" s="71" t="b">
         <f aca="false">AND(IS!G8&gt;0,IS!G8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="H8" s="70" t="b">
+      <c r="H8" s="71" t="b">
         <f aca="false">AND(IS!H8&gt;0,IS!H8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="70" t="b">
+      <c r="I8" s="71" t="b">
         <f aca="false">AND(IS!I8&gt;0,IS!I8&lt;0.6)</f>
         <v>1</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>847</v>
       </c>
     </row>
@@ -55196,11 +55237,11 @@
       <c r="A9" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="B9" s="70" t="b">
+      <c r="B9" s="71" t="b">
         <f aca="false">DCF!D26&gt;0</f>
         <v>1</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="26" t="s">
         <v>849</v>
       </c>
     </row>
@@ -55208,11 +55249,11 @@
       <c r="A10" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="B10" s="70" t="b">
+      <c r="B10" s="71" t="b">
         <f aca="false">ABS(Sensitivity!E8-DCF!D26)&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>851</v>
       </c>
     </row>
@@ -55220,11 +55261,11 @@
       <c r="A11" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="B11" s="70" t="b">
+      <c r="B11" s="71" t="b">
         <f aca="false">OR(ABS(Assumptions!C91-Assumptions!C89)&lt;0.000001,Assumptions!C90&lt;&gt;"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>853</v>
       </c>
     </row>
@@ -55232,27 +55273,27 @@
       <c r="A12" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="E12" s="70" t="b">
+      <c r="E12" s="71" t="b">
         <f aca="false">BS!E4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F12" s="70" t="b">
+      <c r="F12" s="71" t="b">
         <f aca="false">BS!F4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G12" s="70" t="b">
+      <c r="G12" s="71" t="b">
         <f aca="false">BS!G4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H12" s="70" t="b">
+      <c r="H12" s="71" t="b">
         <f aca="false">BS!H4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I12" s="70" t="b">
+      <c r="I12" s="71" t="b">
         <f aca="false">BS!I4&gt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J12" s="27" t="s">
+      <c r="J12" s="26" t="s">
         <v>855</v>
       </c>
     </row>
@@ -55260,27 +55301,27 @@
       <c r="A13" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="E13" s="70" t="b">
+      <c r="E13" s="71" t="b">
         <f aca="false">MIN(FIN!E24,FIN!E32,FIN!E42,FIN!E50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="F13" s="70" t="b">
+      <c r="F13" s="71" t="b">
         <f aca="false">MIN(FIN!F24,FIN!F32,FIN!F42,FIN!F50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="G13" s="70" t="b">
+      <c r="G13" s="71" t="b">
         <f aca="false">MIN(FIN!G24,FIN!G32,FIN!G42,FIN!G50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="H13" s="70" t="b">
+      <c r="H13" s="71" t="b">
         <f aca="false">MIN(FIN!H24,FIN!H32,FIN!H42,FIN!H50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="I13" s="70" t="b">
+      <c r="I13" s="71" t="b">
         <f aca="false">MIN(FIN!I24,FIN!I32,FIN!I42,FIN!I50)&gt;=-0.01</f>
         <v>1</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>857</v>
       </c>
     </row>
@@ -55288,27 +55329,27 @@
       <c r="A14" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="E14" s="70" t="b">
+      <c r="E14" s="71" t="b">
         <f aca="false">FIN!E139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="F14" s="70" t="b">
+      <c r="F14" s="71" t="b">
         <f aca="false">FIN!F139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="G14" s="70" t="b">
+      <c r="G14" s="71" t="b">
         <f aca="false">FIN!G139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="H14" s="70" t="b">
+      <c r="H14" s="71" t="b">
         <f aca="false">FIN!H139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="I14" s="70" t="b">
+      <c r="I14" s="71" t="b">
         <f aca="false">FIN!I139&lt;0.01</f>
         <v>1</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>859</v>
       </c>
     </row>
@@ -55316,11 +55357,11 @@
       <c r="A15" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="B15" s="70" t="b">
+      <c r="B15" s="71" t="b">
         <f aca="true">AND(ISNUMBER(INDIRECT("SCEN_SWITCH")),ISNUMBER(INDIRECT("WACC_USED")),ISNUMBER(INDIRECT("WACC_CALC")),ISNUMBER(INDIRECT("TERM_G")),ISNUMBER(INDIRECT("KE")),ISNUMBER(INDIRECT("KD")),ISNUMBER(INDIRECT("RF_RATE")),ISNUMBER(INDIRECT("ERP")),ISNUMBER(INDIRECT("BETA_U")),ISNUMBER(INDIRECT("TAX_RATE_Y1")),ISNUMBER(INDIRECT("PAYOUT_Y1")),ISNUMBER(INDIRECT("MIN_CASH_PCT")),ISNUMBER(INDIRECT("SHARES_DIL")),ISNUMBER(INDIRECT("DCF_PS")),ISNUMBER(INDIRECT("FCFE_PS")))</f>
         <v>1</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="26" t="s">
         <v>861</v>
       </c>
     </row>
@@ -55328,11 +55369,11 @@
       <c r="A16" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="B16" s="70" t="b">
+      <c r="B16" s="71" t="b">
         <f aca="false">AND(Scenarios!B12&lt;=Scenarios!B21,Scenarios!B21&lt;=Scenarios!B30,Scenarios!B13&lt;=Scenarios!B22,Scenarios!B22&lt;=Scenarios!B31)</f>
         <v>1</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>863</v>
       </c>
     </row>
@@ -55340,27 +55381,27 @@
       <c r="A18" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="E18" s="71" t="n">
+      <c r="E18" s="72" t="n">
         <f aca="false">PPE!E20</f>
         <v>0.162226732338728</v>
       </c>
-      <c r="F18" s="71" t="n">
+      <c r="F18" s="72" t="n">
         <f aca="false">PPE!F20</f>
         <v>0.1432709892243</v>
       </c>
-      <c r="G18" s="71" t="n">
+      <c r="G18" s="72" t="n">
         <f aca="false">PPE!G20</f>
         <v>0.1356267154591</v>
       </c>
-      <c r="H18" s="71" t="n">
+      <c r="H18" s="72" t="n">
         <f aca="false">PPE!H20</f>
         <v>0.131889508814853</v>
       </c>
-      <c r="I18" s="71" t="n">
+      <c r="I18" s="72" t="n">
         <f aca="false">PPE!I20</f>
         <v>0.129505370409207</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>865</v>
       </c>
     </row>
@@ -55372,7 +55413,7 @@
         <f aca="false">IS!E4/Assumptions!$C$12</f>
         <v>0.993078571509739</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>867</v>
       </c>
     </row>
@@ -55397,7 +55438,7 @@
         <f aca="false">Assumptions!C91</f>
         <v>0.0756195390944878</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>870</v>
       </c>
     </row>
@@ -55413,7 +55454,7 @@
         <f aca="false">FCFE!D20</f>
         <v>325.450783525894</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>872</v>
       </c>
     </row>
@@ -55421,11 +55462,11 @@
       <c r="A23" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="B23" s="69" t="str">
+      <c r="B23" s="70" t="str">
         <f aca="false">IF(""&lt;&gt;"","WAIVED: ",IF(ABS(FCFE!D22)&gt;=0.3,"警告: 差异≥30%, 复核债务调度/资本结构/终值","通过: 差异&lt;30%"))</f>
         <v>通过: 差异&lt;30%</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>874</v>
       </c>
     </row>
@@ -55441,7 +55482,7 @@
         <f aca="false">Scenarios!B34</f>
         <v>340.415208186145</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>876</v>
       </c>
     </row>
@@ -55449,11 +55490,11 @@
       <c r="A25" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="B25" s="69" t="str">
+      <c r="B25" s="70" t="str">
         <f aca="false">IF(ABS(Scenarios!B36-1)&gt;=0.3,"警告: 桥接差异≥30%, 复核简化假设","通过: 桥接差异&lt;30%")</f>
         <v>通过: 桥接差异&lt;30%</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>878</v>
       </c>
     </row>
@@ -55469,24 +55510,24 @@
         <f aca="false">FIN!I13</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="73" t="s">
         <v>881</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="str">
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="str">
         <f aca="false">IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15,B16),"全部通过=TRUE","存在未通过=FALSE")</f>
         <v>全部通过=TRUE</v>
       </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
@@ -55523,7 +55564,7 @@
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="10.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.39"/>
   </cols>
@@ -55696,15 +55737,15 @@
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">Relative_Val!C18</f>
-        <v>417.231279393019</v>
+        <v>296.466292691972</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">(C9+D9)/2</f>
-        <v>356.848786042495</v>
+        <v>296.466292691972</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">E9/Assumptions!$C$7-1</f>
-        <v>0.324950009440075</v>
+        <v>0.1007548089406</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>63</v>
@@ -55723,15 +55764,15 @@
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">Relative_Val!D19</f>
-        <v>456.994424835064</v>
+        <v>324.72024415056</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">(C10+D10)/2</f>
-        <v>390.857334492812</v>
+        <v>324.72024415056</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">E10/Assumptions!$C$7-1</f>
-        <v>0.451220935257164</v>
+        <v>0.205659392383171</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>65</v>
@@ -55781,7 +55822,7 @@
         <v>269.33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>70</v>
       </c>
@@ -55801,21 +55842,21 @@
         <f aca="false">E13/Assumptions!$C$7-1</f>
         <v>0.299834654872259</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -55826,102 +55867,102 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D5-C5)/10,0)))&amp;"  ["&amp;TEXT(C5,"0")&amp;"—"&amp;TEXT(D5,"0")&amp;"]"</f>
         <v>▮  [340—340]</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="28" t="str">
+      <c r="B18" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D6-C6)/10,0)))&amp;"  ["&amp;TEXT(C6,"0")&amp;"—"&amp;TEXT(D6,"0")&amp;"]"</f>
         <v>▮  [131—131]</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B19" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D7-C7)/10,0)))&amp;"  ["&amp;TEXT(C7,"0")&amp;"—"&amp;TEXT(D7,"0")&amp;"]"</f>
         <v>▮  [350—350]</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="28" t="str">
+      <c r="B20" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D8-C8)/10,0)))&amp;"  ["&amp;TEXT(C8,"0")&amp;"—"&amp;TEXT(D8,"0")&amp;"]"</f>
         <v>▮  [569—569]</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D9-C9)/10,0)))&amp;"  ["&amp;TEXT(C9,"0")&amp;"—"&amp;TEXT(D9,"0")&amp;"]"</f>
-        <v>▮▮▮▮▮▮▮▮▮▮▮▮  [296—417]</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
+        <v>▮  [296—296]</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D10-C10)/10,0)))&amp;"  ["&amp;TEXT(C10,"0")&amp;"—"&amp;TEXT(D10,"0")&amp;"]"</f>
-        <v>▮▮▮▮▮▮▮▮▮▮▮▮▮  [325—457]</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
+        <v>▮  [325—325]</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="28" t="str">
+      <c r="B23" s="27" t="str">
         <f aca="false">REPT("▮",MAX(1,ROUND((D11-C11)/10,0)))&amp;"  ["&amp;TEXT(C11,"0")&amp;"—"&amp;TEXT(D11,"0")&amp;"]"</f>
         <v>▮  [325—325]</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -56033,18 +56074,18 @@
       <c r="J2" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -56067,7 +56108,7 @@
       <c r="C6" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="28" t="s">
         <v>94</v>
       </c>
     </row>
@@ -56110,23 +56151,23 @@
         <f aca="false">C7*C8</f>
         <v>264751.39</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="28" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
@@ -56241,18 +56282,18 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
@@ -56408,18 +56449,18 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
@@ -56500,18 +56541,18 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
@@ -56736,18 +56777,18 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
@@ -56906,18 +56947,18 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
     </row>
     <row r="54" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
@@ -57016,18 +57057,18 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
@@ -57070,18 +57111,18 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="26" t="s">
+      <c r="A65" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="26"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
@@ -57295,23 +57336,23 @@
       <c r="C77" s="36" t="n">
         <v>6445.6</v>
       </c>
-      <c r="H77" s="25" t="s">
+      <c r="H77" s="28" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="26" t="s">
+      <c r="A79" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="26"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
@@ -57352,7 +57393,7 @@
         <f aca="false">Relative_Val!$O$10</f>
         <v>1.010828480948</v>
       </c>
-      <c r="H82" s="25" t="s">
+      <c r="H82" s="28" t="s">
         <v>226</v>
       </c>
     </row>
@@ -57367,7 +57408,7 @@
         <f aca="false">C77/(C77+C9)</f>
         <v>0.0237672254400759</v>
       </c>
-      <c r="H83" s="25" t="s">
+      <c r="H83" s="28" t="s">
         <v>228</v>
       </c>
     </row>
@@ -57382,7 +57423,7 @@
         <f aca="false">C83/(1-C83)</f>
         <v>0.0243458589584742</v>
       </c>
-      <c r="H84" s="27" t="s">
+      <c r="H84" s="26" t="s">
         <v>230</v>
       </c>
     </row>
@@ -57397,7 +57438,7 @@
         <f aca="false">C82*(1+(1-C41)*C84)</f>
         <v>1.03186959287026</v>
       </c>
-      <c r="H85" s="27" t="s">
+      <c r="H85" s="26" t="s">
         <v>232</v>
       </c>
     </row>
@@ -57426,7 +57467,7 @@
         <f aca="false">C80+C85*C81+C86</f>
         <v>0.0767528276078642</v>
       </c>
-      <c r="H87" s="27" t="s">
+      <c r="H87" s="26" t="s">
         <v>236</v>
       </c>
     </row>
@@ -57455,7 +57496,7 @@
         <f aca="false">(1-C83)*C87+C83*C88*(1-C41)</f>
         <v>0.0756195390944878</v>
       </c>
-      <c r="H89" s="25" t="s">
+      <c r="H89" s="28" t="s">
         <v>240</v>
       </c>
     </row>
@@ -57467,7 +57508,7 @@
         <v>126</v>
       </c>
       <c r="C90" s="38"/>
-      <c r="H90" s="25" t="s">
+      <c r="H90" s="28" t="s">
         <v>242</v>
       </c>
     </row>
@@ -57482,7 +57523,7 @@
         <f aca="false">IF(C90="",C89,C90)</f>
         <v>0.0756195390944878</v>
       </c>
-      <c r="H91" s="25" t="s">
+      <c r="H91" s="28" t="s">
         <v>244</v>
       </c>
     </row>
@@ -57501,18 +57542,18 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="26" t="s">
+      <c r="A94" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
-      <c r="D94" s="26"/>
-      <c r="E94" s="26"/>
-      <c r="F94" s="26"/>
-      <c r="G94" s="26"/>
-      <c r="H94" s="26"/>
-      <c r="I94" s="26"/>
-      <c r="J94" s="26"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="25"/>
+      <c r="J94" s="25"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
@@ -57538,7 +57579,7 @@
       <c r="D96" s="38" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H96" s="27" t="s">
+      <c r="H96" s="26" t="s">
         <v>253</v>
       </c>
     </row>
@@ -57552,7 +57593,7 @@
       <c r="D97" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H97" s="27" t="s">
+      <c r="H97" s="26" t="s">
         <v>255</v>
       </c>
     </row>
@@ -57566,7 +57607,7 @@
       <c r="D98" s="38" t="n">
         <v>0.015</v>
       </c>
-      <c r="H98" s="27" t="s">
+      <c r="H98" s="26" t="s">
         <v>257</v>
       </c>
     </row>
@@ -57682,7 +57723,7 @@
       <c r="D4" s="36" t="n">
         <v>19292.3</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>266</v>
       </c>
     </row>
@@ -57770,7 +57811,7 @@
         <f aca="false">I6/I29</f>
         <v>0.694610551341772</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>270</v>
       </c>
     </row>
@@ -57807,7 +57848,7 @@
         <f aca="false">(Assumptions!G$23+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v>0.14</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>273</v>
       </c>
     </row>
@@ -57878,7 +57919,7 @@
         <f aca="false">(Assumptions!G$30+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v>0.4</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>276</v>
       </c>
     </row>
@@ -57934,18 +57975,18 @@
       <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
@@ -58017,7 +58058,7 @@
         <f aca="false">I14/I29</f>
         <v>0.251762255874286</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>270</v>
       </c>
     </row>
@@ -58054,7 +58095,7 @@
         <f aca="false">(Assumptions!G$25+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v>0.08</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>273</v>
       </c>
     </row>
@@ -58125,7 +58166,7 @@
         <f aca="false">(Assumptions!G$31+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v>0.25</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>276</v>
       </c>
     </row>
@@ -58181,18 +58222,18 @@
       <c r="J20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
@@ -58264,7 +58305,7 @@
         <f aca="false">I22/I29</f>
         <v>0.0536271927839419</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>270</v>
       </c>
     </row>
@@ -58301,7 +58342,7 @@
         <f aca="false">(Assumptions!G$27+CHOOSE(Assumptions!$C$5,Assumptions!$C$96,Assumptions!$C$97,Assumptions!$C$98))</f>
         <v>0.04</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>273</v>
       </c>
     </row>
@@ -58338,7 +58379,7 @@
         <f aca="false">(Assumptions!G$32+CHOOSE(Assumptions!$C$5,Assumptions!$D$96,Assumptions!$D$97,Assumptions!$D$98))</f>
         <v>0.38</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>276</v>
       </c>
     </row>
@@ -58394,18 +58435,18 @@
       <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
@@ -58552,18 +58593,18 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
@@ -58732,18 +58773,18 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
@@ -58938,7 +58979,7 @@
         <f aca="false">Revenue_Segments!I29</f>
         <v>91025.2143659201</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>304</v>
       </c>
     </row>
@@ -58974,7 +59015,7 @@
         <f aca="false">I4/H4-1</f>
         <v>0.118586613634413</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>306</v>
       </c>
     </row>
@@ -59011,7 +59052,7 @@
         <f aca="false">I4-Revenue_Segments!I30</f>
         <v>58150.2641504627</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>308</v>
       </c>
     </row>
@@ -59051,7 +59092,7 @@
         <f aca="false">I4-I6</f>
         <v>32874.9502154573</v>
       </c>
-      <c r="J7" s="25"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
@@ -59089,7 +59130,7 @@
         <f aca="false">I7/I4</f>
         <v>0.361163117763178</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="26" t="s">
         <v>310</v>
       </c>
     </row>
@@ -59126,7 +59167,7 @@
         <f aca="false">I4*Assumptions!G$35</f>
         <v>300.383207407536</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>312</v>
       </c>
     </row>
@@ -59163,7 +59204,7 @@
         <f aca="false">I4*Assumptions!G$36</f>
         <v>1137.815179574</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>314</v>
       </c>
     </row>
@@ -59200,7 +59241,7 @@
         <f aca="false">I4*Assumptions!G$37</f>
         <v>2184.60514478208</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>316</v>
       </c>
     </row>
@@ -59237,7 +59278,7 @@
         <f aca="false">I4*Assumptions!G$38</f>
         <v>3732.03378900272</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>318</v>
       </c>
     </row>
@@ -59274,7 +59315,7 @@
         <f aca="false">FIN!I67</f>
         <v>9.36369974355002</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>320</v>
       </c>
     </row>
@@ -59311,7 +59352,7 @@
         <f aca="false">Assumptions!G$39</f>
         <v>-20</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>322</v>
       </c>
     </row>
@@ -59351,7 +59392,7 @@
         <f aca="false">I7-I9-I10-I11-I12-I13+I14</f>
         <v>25490.7491949474</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -59386,7 +59427,7 @@
         <f aca="false">Assumptions!G$40</f>
         <v>-35</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="26" t="s">
         <v>155</v>
       </c>
     </row>
@@ -59426,7 +59467,7 @@
         <f aca="false">I15+I16</f>
         <v>25455.7491949474</v>
       </c>
-      <c r="J17" s="25"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
@@ -59461,7 +59502,7 @@
         <f aca="false">I17*Assumptions!G$41</f>
         <v>3691.08363326738</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>326</v>
       </c>
     </row>
@@ -59501,7 +59542,7 @@
         <f aca="false">I17-I18</f>
         <v>21764.6655616801</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>328</v>
       </c>
     </row>
@@ -59538,7 +59579,7 @@
         <f aca="false">I19*(1-Assumptions!G$42)</f>
         <v>21764.6655616801</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>330</v>
       </c>
     </row>
@@ -59578,7 +59619,7 @@
         <f aca="false">I19-I20</f>
         <v>0</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>332</v>
       </c>
     </row>
@@ -59618,7 +59659,7 @@
         <f aca="false">I20/I4</f>
         <v>0.239105897341658</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="26" t="s">
         <v>334</v>
       </c>
     </row>
@@ -59658,7 +59699,7 @@
         <f aca="false">I20/Equity_Roll!$C$21</f>
         <v>22.1410636436216</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>336</v>
       </c>
     </row>
@@ -59698,7 +59739,7 @@
         <f aca="false">I17+I13</f>
         <v>25465.112894691</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>338</v>
       </c>
     </row>
@@ -59823,7 +59864,7 @@
         <f aca="false">FIN!I63</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>342</v>
       </c>
     </row>
@@ -59860,7 +59901,7 @@
         <f aca="false">FIN!I61</f>
         <v>30634.9714378481</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>344</v>
       </c>
     </row>
@@ -59897,7 +59938,7 @@
         <f aca="false">Assumptions!G$46/365*IS!I4</f>
         <v>26185.3356395113</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>346</v>
       </c>
     </row>
@@ -59934,7 +59975,7 @@
         <f aca="false">IS!I4*Assumptions!G$49</f>
         <v>364.10085746368</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>348</v>
       </c>
     </row>
@@ -59971,7 +60012,7 @@
         <f aca="false">H8</f>
         <v>352.1</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60008,7 +60049,7 @@
         <f aca="false">Assumptions!G$47/365*IS!I6</f>
         <v>13541.8423364091</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>352</v>
       </c>
     </row>
@@ -60045,7 +60086,7 @@
         <f aca="false">H10</f>
         <v>443.4</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>354</v>
       </c>
     </row>
@@ -60085,7 +60126,7 @@
         <f aca="false">I4+I5+I6+I7+I8+I9+I10</f>
         <v>73342.2545585506</v>
       </c>
-      <c r="J11" s="25"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
@@ -60120,7 +60161,7 @@
         <f aca="false">PPE!I18</f>
         <v>41737.6153102685</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>357</v>
       </c>
     </row>
@@ -60157,7 +60198,7 @@
         <f aca="false">H13</f>
         <v>98.1</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60194,7 +60235,7 @@
         <f aca="false">Schedules!I23</f>
         <v>632.3887215104</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>360</v>
       </c>
     </row>
@@ -60231,7 +60272,7 @@
         <f aca="false">H15</f>
         <v>1193.5</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60268,7 +60309,7 @@
         <f aca="false">H16</f>
         <v>210.9</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60305,7 +60346,7 @@
         <f aca="false">H17</f>
         <v>343.3</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60342,7 +60383,7 @@
         <f aca="false">H18</f>
         <v>2854.3</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>365</v>
       </c>
     </row>
@@ -60379,7 +60420,7 @@
         <f aca="false">H19</f>
         <v>3296.9</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="26" t="s">
         <v>367</v>
       </c>
     </row>
@@ -60419,7 +60460,7 @@
         <f aca="false">I12+I13+I14+I15+I16+I17+I18+I19</f>
         <v>50367.0040317789</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
@@ -60457,7 +60498,7 @@
         <f aca="false">I11+I20</f>
         <v>123709.258590329</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>370</v>
       </c>
     </row>
@@ -60494,7 +60535,7 @@
         <f aca="false">FIN!I24</f>
         <v>0</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>372</v>
       </c>
     </row>
@@ -60531,7 +60572,7 @@
         <f aca="false">Assumptions!G$48/365*IS!I6</f>
         <v>41422.1059701926</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>374</v>
       </c>
     </row>
@@ -60568,7 +60609,7 @@
         <f aca="false">H24</f>
         <v>11.4</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60605,7 +60646,7 @@
         <f aca="false">IS!I4*Assumptions!G$50</f>
         <v>1274.35300112288</v>
       </c>
-      <c r="J25" s="25" t="s">
+      <c r="J25" s="28" t="s">
         <v>377</v>
       </c>
     </row>
@@ -60642,7 +60683,7 @@
         <f aca="false">IS!I4*Assumptions!G$51</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>379</v>
       </c>
     </row>
@@ -60679,7 +60720,7 @@
         <f aca="false">H27</f>
         <v>238.3</v>
       </c>
-      <c r="J27" s="25" t="s">
+      <c r="J27" s="28" t="s">
         <v>350</v>
       </c>
     </row>
@@ -60716,7 +60757,7 @@
         <f aca="false">FIN!I32</f>
         <v>0</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="J28" s="28" t="s">
         <v>382</v>
       </c>
     </row>
@@ -60753,7 +60794,7 @@
         <f aca="false">H29</f>
         <v>16.9</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>384</v>
       </c>
     </row>
@@ -60793,7 +60834,7 @@
         <f aca="false">I22+I23+I24+I25+I26+I27+I28+I29</f>
         <v>44783.5632586339</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
@@ -60828,7 +60869,7 @@
         <f aca="false">FIN!I42</f>
         <v>0</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J31" s="28" t="s">
         <v>387</v>
       </c>
     </row>
@@ -60865,7 +60906,7 @@
         <f aca="false">FIN!I50</f>
         <v>0</v>
       </c>
-      <c r="J32" s="25" t="s">
+      <c r="J32" s="28" t="s">
         <v>382</v>
       </c>
     </row>
@@ -60902,7 +60943,7 @@
         <f aca="false">H33</f>
         <v>638.3</v>
       </c>
-      <c r="J33" s="25" t="s">
+      <c r="J33" s="28" t="s">
         <v>390</v>
       </c>
     </row>
@@ -60942,7 +60983,7 @@
         <f aca="false">I31+I32+I33</f>
         <v>638.3</v>
       </c>
-      <c r="J34" s="25"/>
+      <c r="J34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
@@ -61014,7 +61055,7 @@
         <f aca="false">Equity_Roll!I5</f>
         <v>870.3</v>
       </c>
-      <c r="J36" s="25" t="s">
+      <c r="J36" s="28" t="s">
         <v>394</v>
       </c>
     </row>
@@ -61051,7 +61092,7 @@
         <f aca="false">Equity_Roll!I6</f>
         <v>5387.3</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="28" t="s">
         <v>394</v>
       </c>
     </row>
@@ -61088,7 +61129,7 @@
         <f aca="false">Equity_Roll!I7</f>
         <v>5.4</v>
       </c>
-      <c r="J38" s="25" t="s">
+      <c r="J38" s="28" t="s">
         <v>394</v>
       </c>
     </row>
@@ -61125,7 +61166,7 @@
         <f aca="false">Equity_Roll!I8</f>
         <v>1994.3</v>
       </c>
-      <c r="J39" s="25" t="s">
+      <c r="J39" s="28" t="s">
         <v>394</v>
       </c>
     </row>
@@ -61162,7 +61203,7 @@
         <f aca="false">Equity_Roll!I10</f>
         <v>8538.68509474164</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="J40" s="28" t="s">
         <v>399</v>
       </c>
     </row>
@@ -61199,7 +61240,7 @@
         <f aca="false">Equity_Roll!I12</f>
         <v>61493.1102369538</v>
       </c>
-      <c r="J41" s="25" t="s">
+      <c r="J41" s="28" t="s">
         <v>401</v>
       </c>
     </row>
@@ -61236,7 +61277,7 @@
         <f aca="false">H42</f>
         <v>9.1</v>
       </c>
-      <c r="J42" s="25" t="s">
+      <c r="J42" s="28" t="s">
         <v>403</v>
       </c>
     </row>
@@ -61310,7 +61351,7 @@
         <f aca="false">H44</f>
         <v>0</v>
       </c>
-      <c r="J44" s="25" t="s">
+      <c r="J44" s="28" t="s">
         <v>406</v>
       </c>
     </row>
@@ -61424,7 +61465,7 @@
         <f aca="false">I21-I46</f>
         <v>0</v>
       </c>
-      <c r="J47" s="25" t="s">
+      <c r="J47" s="28" t="s">
         <v>410</v>
       </c>
     </row>
@@ -61549,7 +61590,7 @@
         <f aca="false">IS!I20</f>
         <v>21764.6655616801</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="28" t="s">
         <v>413</v>
       </c>
     </row>
@@ -61586,7 +61627,7 @@
         <f aca="false">PPE!I19</f>
         <v>4646.05484871961</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="28" t="s">
         <v>415</v>
       </c>
     </row>
@@ -61623,7 +61664,7 @@
         <f aca="false">FIN!I64</f>
         <v>0.0517499999999999</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>417</v>
       </c>
     </row>
@@ -61660,7 +61701,7 @@
         <f aca="false">-Schedules!I18</f>
         <v>-238.154185168642</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>419</v>
       </c>
     </row>
@@ -61697,7 +61738,7 @@
         <f aca="false">I4+I5+I6+I7</f>
         <v>26172.617975231</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>421</v>
       </c>
     </row>
@@ -61734,7 +61775,7 @@
         <f aca="false">-PPE!I14</f>
         <v>-8192.26929293281</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>423</v>
       </c>
     </row>
@@ -61771,7 +61812,7 @@
         <f aca="false">PPE!I9</f>
         <v>354.507655597858</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>425</v>
       </c>
     </row>
@@ -61808,7 +61849,7 @@
         <f aca="false">-FIN!I62</f>
         <v>-12126.4572960851</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>427</v>
       </c>
     </row>
@@ -61845,7 +61886,7 @@
         <f aca="false">I9+I10+I11</f>
         <v>-19964.2189334201</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>429</v>
       </c>
     </row>
@@ -61882,7 +61923,7 @@
         <f aca="false">FIN!I57</f>
         <v>-2.3</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>431</v>
       </c>
     </row>
@@ -61919,7 +61960,7 @@
         <f aca="false">-FIN!I64</f>
         <v>-0.0517499999999999</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>433</v>
       </c>
     </row>
@@ -61956,7 +61997,7 @@
         <f aca="false">-Schedules!I26</f>
         <v>-6013.04709324918</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>435</v>
       </c>
     </row>
@@ -61993,7 +62034,7 @@
         <f aca="false">I13+I14+I15</f>
         <v>-6015.39884324918</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="28" t="s">
         <v>437</v>
       </c>
     </row>
@@ -62030,7 +62071,7 @@
         <f aca="false">I8+I12+I16</f>
         <v>193.000198561806</v>
       </c>
-      <c r="J17" s="25"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
@@ -62065,7 +62106,7 @@
         <f aca="false">H19</f>
         <v>1627.5040887566</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="26" t="s">
         <v>440</v>
       </c>
     </row>
@@ -62102,7 +62143,7 @@
         <f aca="false">I18+I17</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>442</v>
       </c>
     </row>
@@ -62195,18 +62236,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -62244,7 +62285,7 @@
         <f aca="false">BS!I6</f>
         <v>26185.3356395113</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>446</v>
       </c>
     </row>
@@ -62284,7 +62325,7 @@
         <f aca="false">BS!I7</f>
         <v>364.10085746368</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>447</v>
       </c>
     </row>
@@ -62324,7 +62365,7 @@
         <f aca="false">BS!I8</f>
         <v>352.1</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>448</v>
       </c>
     </row>
@@ -62364,7 +62405,7 @@
         <f aca="false">BS!I9</f>
         <v>13541.8423364091</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>449</v>
       </c>
     </row>
@@ -62404,7 +62445,7 @@
         <f aca="false">SUM(I6:I9)</f>
         <v>40443.3788333841</v>
       </c>
-      <c r="J10" s="25"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
@@ -62442,7 +62483,7 @@
         <f aca="false">BS!I23</f>
         <v>41422.1059701926</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="28" t="s">
         <v>451</v>
       </c>
     </row>
@@ -62482,7 +62523,7 @@
         <f aca="false">BS!I24</f>
         <v>11.4</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="28" t="s">
         <v>452</v>
       </c>
     </row>
@@ -62522,7 +62563,7 @@
         <f aca="false">BS!I25</f>
         <v>1274.35300112288</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="28" t="s">
         <v>453</v>
       </c>
     </row>
@@ -62562,7 +62603,7 @@
         <f aca="false">BS!I26</f>
         <v>1820.5042873184</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>453</v>
       </c>
     </row>
@@ -62602,7 +62643,7 @@
         <f aca="false">BS!I27</f>
         <v>238.3</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>452</v>
       </c>
     </row>
@@ -62642,7 +62683,7 @@
         <f aca="false">SUM(I11:I15)</f>
         <v>44766.6632586339</v>
       </c>
-      <c r="J16" s="25"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
@@ -62680,7 +62721,7 @@
         <f aca="false">I10-I16</f>
         <v>-4323.28442524986</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="28" t="s">
         <v>456</v>
       </c>
     </row>
@@ -62708,23 +62749,23 @@
         <f aca="false">I17-H17</f>
         <v>238.154185168642</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="26" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>459</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
@@ -62750,7 +62791,7 @@
         <f aca="false">H23</f>
         <v>687.37904512</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="26" t="s">
         <v>461</v>
       </c>
     </row>
@@ -62778,7 +62819,7 @@
         <f aca="false">I21*Assumptions!$C$59</f>
         <v>54.9903236096</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="28" t="s">
         <v>463</v>
       </c>
     </row>
@@ -62806,23 +62847,23 @@
         <f aca="false">I21-I22</f>
         <v>632.3887215104</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="28" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
@@ -62848,7 +62889,7 @@
         <f aca="false">IS!H20*Assumptions!G$62</f>
         <v>6013.04709324918</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J26" s="28" t="s">
         <v>468</v>
       </c>
     </row>
@@ -62944,18 +62985,18 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>471</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
@@ -62980,7 +63021,7 @@
         <f aca="false">H10</f>
         <v>35450.7655597858</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>473</v>
       </c>
     </row>
@@ -63008,7 +63049,7 @@
         <f aca="false">(I13+I14)*Assumptions!$C$55</f>
         <v>8424.31644839288</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="28" t="s">
         <v>475</v>
       </c>
     </row>
@@ -63036,7 +63077,7 @@
         <f aca="false">I6*Assumptions!$C$56+I7*Assumptions!$C$57</f>
         <v>4591.06452511001</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="28" t="s">
         <v>477</v>
       </c>
     </row>
@@ -63064,7 +63105,7 @@
         <f aca="false">I6*Assumptions!$C$58</f>
         <v>354.507655597858</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="28" t="s">
         <v>479</v>
       </c>
     </row>
@@ -63092,23 +63133,23 @@
         <f aca="false">I6+I7-I8-I9</f>
         <v>38929.5098274708</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="28" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -63133,7 +63174,7 @@
         <f aca="false">H15</f>
         <v>3040.1526382577</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>484</v>
       </c>
     </row>
@@ -63161,7 +63202,7 @@
         <f aca="false">IS!I4*Assumptions!G$54</f>
         <v>8192.26929293281</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="28" t="s">
         <v>486</v>
       </c>
     </row>
@@ -63189,23 +63230,23 @@
         <f aca="false">I13+I14-I7</f>
         <v>2808.10548279763</v>
       </c>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="28" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>489</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
@@ -63243,7 +63284,7 @@
         <f aca="false">I10+I15</f>
         <v>41737.6153102685</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="J18" s="28" t="s">
         <v>491</v>
       </c>
     </row>
@@ -63283,7 +63324,7 @@
         <f aca="false">I8+Schedules!I22</f>
         <v>4646.05484871961</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="28" t="s">
         <v>493</v>
       </c>
     </row>
@@ -63311,7 +63352,7 @@
         <f aca="false">I8/I6</f>
         <v>0.129505370409207</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="28" t="s">
         <v>495</v>
       </c>
     </row>
@@ -63339,7 +63380,7 @@
         <f aca="false">I6/I8</f>
         <v>7.72168750099114</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="J21" s="28" t="s">
         <v>497</v>
       </c>
     </row>
